--- a/01-dida/技术要求V1.1.xlsx
+++ b/01-dida/技术要求V1.1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28580" windowHeight="15840" activeTab="2"/>
+    <workbookView windowWidth="27000" windowHeight="12240"/>
   </bookViews>
   <sheets>
     <sheet name="（一）MDC数据采集平台" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="339">
   <si>
     <t>（一）MDC数据采集平台（数量：1套）
 1.功能要求：基于学校现有设备及接口开放的数据，利用信息化、物联网技术，控制器、机床物联模块、数控采集卡等硬件，将各机床设备与计算机、智能终端等设备互通互联。为实训楼一楼的100（台/套）设备进行数据采集，其中包含不少于10个5G数据采集终端，包含30套机床视频采集展示系统并集成到数据采集系统中能随时调用。
@@ -26,930 +26,264 @@
 4.各项指标要求：</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>指标项</t>
+  </si>
+  <si>
+    <t>指标要求</t>
+  </si>
+  <si>
+    <t>方案覆盖</t>
+  </si>
+  <si>
+    <t>详细描述</t>
+  </si>
+  <si>
+    <t>MDC数据采集系统</t>
+  </si>
+  <si>
+    <t>1.功能与效果：</t>
+  </si>
+  <si>
+    <t>1) 准确统计设备OEE：能够实时了解设备运行情况以及学生使用情况；</t>
+  </si>
+  <si>
+    <t>2) 实验实训报工数据匹配校核：通过设备采集的运行数据与学生基于智能工厂管控平台报工数据形成关联对比，实现实验实训报工工时有效分析，为进一步深入学生实操成绩考核提供数据支撑。</t>
+  </si>
+  <si>
+    <t>2.实时监控</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1) #车间概况：对现场设备进行建模，显示车间设备运行状态：实时当前状态、状态持续时长、当天运行时长、当天稼动率，柱形图显示车间设备的7天稼动率，显示车间设备实时状态的统计：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>报警</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、运行、空闲、关机、调试，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>显示实时设备报警信息</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（提供对应功能截图加盖投标人公章）</t>
+    </r>
+  </si>
+  <si>
+    <t>2) 设备详情：可配置的组件化模型显示设备实时运行数据、设备示意图联动实时参数标签显示、主轴转速仪表盘、主轴倍率、仪表盘、进给仪表盘、设备7天稼动率、设备今日报警、设备实时参数列表、24H设备运行时序图显示；</t>
+  </si>
+  <si>
+    <t>3) 机床内部加工区域监控：不少于30套的机床监控系统，通过机床上方展示看板实时传递机床内部及操作面板运行画面，并可在系统中调取相应的监控内容。</t>
+  </si>
+  <si>
+    <t>3.设备状态分析</t>
+  </si>
+  <si>
+    <t>1) 状态过程监控：车间设备24H运行时序图显示，设备历史周期段的设备运行时序图显示，报表显示并可导出设备运行过程数据：状态、开始时间、结束时间、状态时长；</t>
+  </si>
+  <si>
+    <t>2) 班组用时分析：按照年/月/日或者一段日期区间，图表方式显示车间班组设备运行用时数据，包括报警、运行、空闲、关机、调试的时长和占比，支持数据导出；</t>
+  </si>
+  <si>
+    <t>3) 设备用时分析：统计年/月/日或者一段日期区间，图表方式显示设备的每日或者每月的运行用时数据，支持数据导出。</t>
+  </si>
+  <si>
+    <t>4.设备运营分析</t>
+  </si>
+  <si>
+    <t>1) 设备稼动率监控：</t>
+  </si>
+  <si>
+    <t>统计年/月/日或者一段日期区间，图表方式显示设备稼动率情况，包括运行工时、标准工时、稼动率值、目标值、平均值，支持数据导出。</t>
+  </si>
+  <si>
+    <t>5.设备报警分析</t>
+  </si>
+  <si>
+    <t>1) 提供设备异常报警；</t>
+  </si>
+  <si>
+    <t>2) 统计年/月/日或者一段日期区间，图表方式显示设备报警记录次数，包括设备报警次数统计、报警时间、报警号、报警信息，支持数据导出；</t>
+  </si>
+  <si>
+    <t>6.报警分类表</t>
+  </si>
+  <si>
+    <t>1) 统计年/月/日或者一段日期区间，按照设备报警号归类显示设备的报警信息，包括报警次数、报警内容、饼状图占比分析，支持数据导出。</t>
+  </si>
+  <si>
+    <t>7.综合报表</t>
+  </si>
+  <si>
+    <t>1) 报工数据和采集数据的24H设备运行时序图；</t>
+  </si>
+  <si>
+    <t>2) #加工工时对比表：</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>序号</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>显示智慧工厂管控平台中该设备报工工序信息联动设备数采状态用时，包括：工件名称、工序名称、理论计划工时、实际报工工时、设备实际状态工时；</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
         <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>指标项</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>指标要求</t>
-    </r>
-  </si>
-  <si>
-    <t>MDC数据采集系统</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1.功能与效果：</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>准确统计设备OEE：能够实时了解设备运行情况以及学生使用情况；</t>
-    </r>
-  </si>
-  <si>
-    <t>2) 实验实训报工数据匹配校核：通过设备采集的运行数据与学生基于智能工厂管控平台报工数据形成关联对比，实现实验实训报工工时有效分析，为进一步深入学生实操成绩考核提供数据支撑。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2.实时监控</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1) #车间概况：对现场设备进行建模，显示车间设备运行状态：实时当前状态、状态持续时长、当天运行时长、当天稼动率，柱形图显示车间设备的7天稼动率，显示车间设备实时状态的统计：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（提供对应功能截图加盖投标人公章）</t>
+    </r>
+  </si>
+  <si>
+    <t>3) 双稼动率分析：柱形图显示设备的报工稼动率和数采稼动率。</t>
+  </si>
+  <si>
+    <t>8.设备数据采集：结合已有设备或产线数据接口的开放情况，获取设备的运行数据。</t>
+  </si>
+  <si>
+    <t>1) 数控设备：</t>
+  </si>
+  <si>
+    <t>a) 设备状态：运行、报警、空闲、关机、调试；</t>
+  </si>
+  <si>
+    <t>b) 报警信息：报警信息、报警时间；</t>
+  </si>
+  <si>
+    <t>c) 转速和进给：进给值，进给倍率，主轴转速，主轴倍率；</t>
+  </si>
+  <si>
+    <t>2) 其它普通机床及设备：设备状态：运行、空闲、关机。包含智能产线中设备及机械手状态。</t>
+  </si>
+  <si>
+    <t>9.展示看板，数量10套：</t>
+  </si>
+  <si>
+    <t>1)显示相应区域设备模型，并展现相应设备状态等看板内容。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2)提供≥65寸看板系统，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>报警</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、运行、空闲、关机、调试，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>显示实时设备报警信息</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提供移动式落地支架安装</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>；</t>
     </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（提供对应功能截图加盖投标人公章）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>所有开动率改成稼动率，所有要求的文字保持一致
-图1
-每个设备：大冲A1后面 P加  状态持续时长：xxx
-左侧，红框 框上哪里看 当天运行时长、
-当天稼动率，然后文字箭头过去说明 可查看当天运行时长和当天稼动率
-左侧上角的状态 得改成和要求一致，右边运行的状态，改两个别的状态
-图2：柱形图显示车间设备的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>7天稼动率，红框+ 文字</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-图1左上角，显示车间设备实时状态的统计：报警、运行、空闲、关机、调试——红框+文字
-加一个显示实时设备报警信息，只截图蓝色区域，红框+文字</t>
-    </r>
-  </si>
-  <si>
-    <t>启杨</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>设备详情：可配置的组件化模型显示设备实时运行数据、设备示意图联动实时参数标签显示、主轴转速仪表盘、主轴倍率、仪表盘、进给仪表盘、设备7天稼动率、设备今日报警、设备实时参数列表、24H设备运行时序图显示；</t>
-    </r>
-  </si>
-  <si>
-    <t>3) 机床内部加工区域监控：不少于30套的机床监控系统，通过机床上方展示看板实时传递机床内部及操作面板运行画面，并可在系统中调取相应的监控内容。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3.设备状态分析</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>状态过程监控：车间设备24H运行时序图显示，设备历史周期段的设备运行时序图显示，报表显示并可导出设备运行过程数据：状态、开始时间、结束时间、状态时长；</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>班组用时分析：按照年/月/日或者一段日期区间，图表方式显示车间班组设备运行用时数据，包括报警、运行、空闲、关机、调试的时长和占比，支持数据导出；</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>设备用时分析：统计年/月/日或者一段日期区间，图表方式显示设备的每日或者每月的运行用时数据，支持数据导出。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>4.设备运营分析</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>设备稼动率监控：</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>统计年/月/日或者一段日期区间，图表方式显示设备稼动率情况，包括运行工时、标准工时、稼动率值、目标值、平均值，支持数据导出。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5.设备报警分析</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>提供设备异常报警；</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>统计年/月/日或者一段日期区间，图表方式显示设备报警记录次数，包括设备报警次数统计、报警时间、报警号、报警信息，支持数据导出；</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>6.报警分类表</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>统计年/月/日或者一段日期区间，按照设备报警号归类显示设备的报警信息，包括报警次数、报警内容、饼状图占比分析，支持数据导出。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>7.综合报表</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>报工数据和采集数据的24H设备运行时序图；</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>#加工工时对比表：</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>显示智慧工厂管控平台中该设备报工工序信息联动设备数采状态用时，包括：工件名称、工序名称、理论计划工时、实际报工工时、设备实际状态工时；</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（提供对应功能截图加盖投标人公章）</t>
-    </r>
-  </si>
-  <si>
-    <t>没问题</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>双稼动率分析：柱形图显示设备的报工稼动率和数采稼动率。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>8.设备数据采集：结合已有设备或产线数据接口的开放情况，获取设备的运行数据。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>数控设备：</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>a) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>设备状态：运行、报警、空闲、关机、调试；</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>b) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>报警信息：报警信息、报警时间；</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>c) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>转速和进给：进给值，进给倍率，主轴转速，主轴倍率；</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>其它普通机床及设备：设备状态：运行、空闲、关机。包含智能产线中设备及机械手状态。</t>
-    </r>
-  </si>
-  <si>
-    <t>9.展示看板，数量10套：</t>
-  </si>
-  <si>
-    <t>1、支架额外配也行，要告诉我价格
-2、对照标书的参数，大屏的具体参数是什么，让他们要告诉下</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>显示相应区域设备模型，并展现相应设备状态等看板内容。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2)提供≥65寸看板系统，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>提供移动式落地支架安装</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>；</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>端口参数：HDMI2.0接口数≥1个、USB2.0接口数≥1个；</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>4)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>网络参数：连接方式无线/有线；</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>功耗参数：待机功率≥0.5W、工作电压220V、电源功率≥200W；</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>6)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>外观设计：屏占比95%&gt;N≥90%、安装孔距≥300*300mm；</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>7)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>核心参数：WIFI频段2.4G、运行内存/RAM≥2GB、存储内存≥32GB；</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>8)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>显示参数：屏幕分辨率高清、色域值≥72%、亮度200-300尼特、屏幕尺寸≥65英寸、屏幕比例16:9；</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>9)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>可显示区域内设备加工状态、机器人工作状态等信息，并可统计显示稼动率、设备报警信息等，显示料库信息。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>10.要求采集数据与教学管理平台、智慧工厂工控平台数据共享、互通。</t>
-    </r>
+  </si>
+  <si>
+    <t>3)端口参数：HDMI2.0接口数≥1个、USB2.0接口数≥1个；</t>
+  </si>
+  <si>
+    <t>4)网络参数：连接方式无线/有线；</t>
+  </si>
+  <si>
+    <t>5)功耗参数：待机功率≥0.5W、工作电压220V、电源功率≥200W；</t>
+  </si>
+  <si>
+    <t>6)外观设计：屏占比95%&gt;N≥90%、安装孔距≥300*300mm；</t>
+  </si>
+  <si>
+    <t>7)核心参数：WIFI频段2.4G、运行内存/RAM≥2GB、存储内存≥32GB；</t>
+  </si>
+  <si>
+    <t>8)显示参数：屏幕分辨率高清、色域值≥72%、亮度200-300尼特、屏幕尺寸≥65英寸、屏幕比例16:9；</t>
+  </si>
+  <si>
+    <t>9)可显示区域内设备加工状态、机器人工作状态等信息，并可统计显示稼动率、设备报警信息等，显示料库信息。</t>
+  </si>
+  <si>
+    <t>10.要求采集数据与教学管理平台、智慧工厂工控平台数据共享、互通。</t>
   </si>
   <si>
     <t>数据服务器</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>用于现场数据采集系统及实训系统的数据处理，储存。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>数量：1台</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>处理器配置：≥16核心，32线程，2.0G主频。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>计算内存配置：2条32G，DDR4，RECC内存</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>4. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>存储配置：≥4块960G：SSD固态硬盘 4块</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>网络配置：集成双千兆/万兆网卡</t>
-    </r>
+    <t>用于现场数据采集系统及实训系统的数据处理，储存。</t>
+  </si>
+  <si>
+    <t>1. 数量：1台</t>
+  </si>
+  <si>
+    <t>2. 处理器配置：≥16核心，32线程，2.0G主频。</t>
+  </si>
+  <si>
+    <t>3. 计算内存配置：2条32G，DDR4，RECC内存</t>
+  </si>
+  <si>
+    <t>4. 存储配置：≥4块960G：SSD固态硬盘 4块</t>
+  </si>
+  <si>
+    <t>5. 网络配置：集成双千兆/万兆网卡</t>
   </si>
   <si>
     <t>（二）教学管理平台（数量：1套）
@@ -959,22 +293,7 @@
 4.各项指标要求：</t>
   </si>
   <si>
-    <t>序号</t>
-  </si>
-  <si>
-    <t>指标项</t>
-  </si>
-  <si>
     <t>模块</t>
-  </si>
-  <si>
-    <t>指标要求</t>
-  </si>
-  <si>
-    <t>方案覆盖</t>
-  </si>
-  <si>
-    <t>详细描述</t>
   </si>
   <si>
     <t>首页</t>
@@ -1039,10 +358,18 @@
     <t>1) 提供可视化试题要求编辑平台，支持通过文本编辑器添加文字说明，支持多格式文件（图片、文档等）上传及超链接嵌入功能，实现实训试题要求的多样化、结构化呈现，助力学生全面理解试题目标与规范。</t>
   </si>
   <si>
+    <t>基本覆盖</t>
+  </si>
+  <si>
     <t>2) 可通过系统试题编辑模块，灵活制定实训试题内容，支持创建问答类题目、设置实验（实训）成果提交任务，包括图片、文件等格式的实验过程记录或报告上传要求，实现试题内容的定制化与考核形式的多元化。</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>3) ▲系统创建关联智慧工厂管控平台实验，制定与平台相关联的实验任务如“设计任务”“工艺任务”“编程任务”“检测任务”，设置分数与评分规则。</t>
     </r>
     <r>
@@ -1068,13 +395,13 @@
     <t>5) 支持模板维护与调用功能，方便进行基于模板的快速编辑；</t>
   </si>
   <si>
+    <t>否</t>
+  </si>
+  <si>
     <t>培养计划</t>
   </si>
   <si>
     <t>能针对每个专业各个年级制定不同的培养计划，可根据需要将多个课程组成一个培养计划，也可将一个课程制定成一个培养计划，还可以设置各课程所占学分、学时方便教师根据培养计划教学。</t>
-  </si>
-  <si>
-    <t>否</t>
   </si>
   <si>
     <t>改动点：不需要培养计划，老师是从第三方系统（？？系统）下载课程表后，再导入到咱们系统里</t>
@@ -1104,13 +431,25 @@
     <t>1) 系统支持构建标准化实验信息管理模型，涵盖实验名称、总分、实验成绩、报告成绩、实验课时、实验地点、实验时间、实验类型、实验种类、产品对接、实验环节、实验要求、实验报告等信息。</t>
   </si>
   <si>
+    <t>总分判定规则</t>
+  </si>
+  <si>
     <t>2) 在实验要求中，系统提供文本编辑工具，可通过文字编排、图片上传、文件附件及内外部超链接嵌入等方式，构建图文并茂、资源联动的实验指导说明，提升学生任务理解度。</t>
   </si>
   <si>
     <t>3) 在实验报告中，支持自定义实验报告内容框架与提交要求，包括问题作答、图片上传、文件提交等多类型任务设定，同时可配置报告格式模板，规范学生成果输出标准</t>
   </si>
   <si>
-    <r>
+    <t>报告格式模版？</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>4) #超链接：系统内置超链接管理模块，支持快速关联实验相关资源，包含外部网站、内部教学系统的深度链接。</t>
     </r>
     <r>
@@ -1168,6 +507,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>4) #系统内置标准化数据接口，教师完成综合试卷下发后，可将试卷名称、考试类型等关键信息以订单形式同步至智慧工厂管控平台。实现教学与生产场景的数据协同。</t>
     </r>
     <r>
@@ -1182,10 +527,20 @@
     </r>
   </si>
   <si>
+    <t>1. “设计”、“工艺”、“编程”类任务：
+2. “加工”、“检测”类任务：</t>
+  </si>
+  <si>
     <t>5) 系统支持教师对学生提交的实训考试进行在线阅卷，提供多维度评分工具：可自定义不同考试类型（如理论、实操）在百分制总分中的权重占比；支持手动修改得分功能；阅卷过程支持批量处理与进度跟踪，提升评分效率与准确性。</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>6) #系统与智慧工厂管控平台深度集成，可依据智慧工厂管控平台中的审批信息，触发关联考试的智能评分功能。同时保留教师人工干预权限，支持对自动评分结果进行复核与修正，实现智能化与人工审核的有机结合。</t>
     </r>
     <r>
@@ -1223,6 +578,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>2) #系统提供开放的 API 接口平台和二次开发平台，能支持对系统的二次开发。</t>
     </r>
     <r>
@@ -1238,6 +599,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>3) #系统页面需要具备灵活性，至少应该具备：页面级的调配功能和用户级的调整功能；</t>
     </r>
     <r>
@@ -1259,6 +626,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>1) 支持统一进行订单各项数据的管理，包括</t>
     </r>
     <r>
@@ -1296,6 +669,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>1. 如果是老师现有说的需求，大致不存有以下场景
    1）延期风险：学生过期未提交实训任务后，自动判定 未实训，成绩不良
 2. 状态管理：</t>
@@ -1321,6 +700,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>4) ▲支持实验订单交期预排功能，支持预测订单交期模拟，提供不少于2种工作量选择模式及多种策略设定模式，能反馈订单整体交期情况。</t>
     </r>
     <r>
@@ -1360,6 +745,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>在设计类课程场景下：按照任务分配的方式，分配对应的学生设计任务，能够清晰的获知设计每个阶段任务的完成情况，统计学生的实验任务的进展情况，同时系统可以设定审核机制，在学生完成对应的任务后，可以将对应的设计资料进行上传由实验老师来进行审核，只有</t>
     </r>
     <r>
@@ -1451,6 +842,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>9) #支持web在线查看设计图档，能对图档进行不少于3种方式的操作，放大、缩小、</t>
     </r>
     <r>
@@ -1484,6 +881,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>10) #支持图档管理，具备图档便捷上传、存储、版本的管理及相关图档附属信息显示；</t>
     </r>
     <r>
@@ -1524,6 +927,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>3) #工艺编制具备智能性，便捷性（具备工艺知识库、零件工艺间的复制与粘贴，颜色标识，以及智能检索）</t>
     </r>
     <r>
@@ -1566,6 +975,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>教师
 1. 预估工时：在工艺路线页 维护
 2. 实际工时：各道工序，</t>
@@ -1601,6 +1016,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>10) #具备特色的工艺知识库管理，在编制工艺时可快速提取；支持零件工艺excel批量导入、历史工艺快速复制；</t>
     </r>
     <r>
@@ -1628,6 +1049,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>13) 工艺工序下支持按工步管理零件加工方式，同时</t>
     </r>
     <r>
@@ -1651,6 +1078,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>14) 典型工艺库除可支持工序层级的编辑维护外，同时支持</t>
     </r>
     <r>
@@ -1690,7 +1123,7 @@
   <si>
     <t>编程任务生成的两种方式
 1. 实训试卷发布
-2. 结合工艺任务 自动生成编程任务</t>
+2. 结合工艺任务 自动生成编程任务？是否需要这个</t>
   </si>
   <si>
     <t>1) 支持结合零件制造工艺要求及生产计划紧急程度（按照工序计划上机时间排序）进行编程任务安排；</t>
@@ -1700,6 +1133,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>2) 能够根据工艺要求，自动生成</t>
     </r>
     <r>
@@ -1779,6 +1218,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>9) </t>
     </r>
     <r>
@@ -1846,6 +1291,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>4) #支持结合排程计划和程式清单，提供备刀刀具需求计划明细，包括刀具明细、需求的计划时间、所需求的工序等</t>
     </r>
     <r>
@@ -1903,6 +1354,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>3) #具备品质加密管理功能（品质质检刷卡时，可选择是否需要输入密码，以防止他人盗用）；</t>
     </r>
     <r>
@@ -1945,6 +1402,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>2) ▲支持通过看板配置，实现自动定义轮播看板，可定义轮播看板中每个看板的播放时长，轮播看板可配置选择系统现有自定义看板和第三方免登陆看板地址（http网址）看板管理支持与各功能区以及MDC数据采集对接，将功能区加工过程信息，当前机床加工零件信息，机床数据信息等信息以图形，甘特图等形式展示；</t>
     </r>
     <r>
@@ -1986,6 +1448,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>#13.考虑到系统使用时长及现场设备台套数量较多，数据量相对较大，对于排产运算速度需要有较高要求，需要提供至少30W条及以上数据的第三方测试报告，要求30W条数据运算速度不低于60秒。</t>
     </r>
     <r>
@@ -2003,6 +1470,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>工业型不干胶打印机</t>
     </r>
     <r>
@@ -2021,6 +1494,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>分辨率≥300</t>
     </r>
     <r>
@@ -2044,6 +1523,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>2.具备 LED 红蓝信号指示灯、具备蜂鸣器 、</t>
     </r>
     <r>
@@ -2070,6 +1555,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>#5.兼容 RFID 高频芯片、RFID 低频芯片 / 一维条码、二维码，即插即用，免驱动安装</t>
     </r>
     <r>
@@ -2724,6 +2215,26 @@
   </si>
   <si>
     <t>热敏不干胶条码标签打印机</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数量：1台</t>
+    </r>
   </si>
   <si>
     <r>
@@ -3429,14 +2940,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3464,12 +2975,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.25"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3889,7 +3394,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3913,16 +3418,16 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -3931,89 +3436,89 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4128,64 +3633,46 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4206,92 +3693,38 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -4346,6 +3779,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="00FFFF00"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -4646,385 +4084,466 @@
   <cols>
     <col min="2" max="2" width="15.1923076923077" customWidth="1"/>
     <col min="3" max="3" width="99.1057692307692" customWidth="1"/>
-    <col min="4" max="4" width="54.625" customWidth="1"/>
+    <col min="4" max="4" width="10.4134615384615" customWidth="1"/>
+    <col min="5" max="5" width="53.0384615384615" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="118" customHeight="1" spans="1:5">
-      <c r="A1" s="77" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-    </row>
-    <row r="2" ht="18" spans="1:3">
-      <c r="A2" s="79" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="46" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" ht="18" spans="1:3">
-      <c r="A3" s="79">
+      <c r="D2" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="44">
         <v>1</v>
       </c>
-      <c r="B3" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="82" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" ht="18" spans="1:3">
-      <c r="A4" s="79"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="82" t="s">
+      <c r="B3" s="33" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" ht="53" spans="1:3">
-      <c r="A5" s="79"/>
-      <c r="B5" s="80"/>
-      <c r="C5" s="83" t="s">
+      <c r="C3" s="64" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" ht="18" spans="1:3">
-      <c r="A6" s="79"/>
-      <c r="B6" s="80"/>
-      <c r="C6" s="82" t="s">
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="44"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="64" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" ht="199" customHeight="1" spans="1:5">
-      <c r="A7" s="79"/>
-      <c r="B7" s="80"/>
-      <c r="C7" s="84" t="s">
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+    </row>
+    <row r="5" ht="31" spans="1:5">
+      <c r="A5" s="44"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="85" t="s">
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="44"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="E7" t="s">
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+    </row>
+    <row r="7" ht="46" spans="1:5">
+      <c r="A7" s="44"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="65" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" ht="53" spans="1:3">
-      <c r="A8" s="79"/>
-      <c r="B8" s="80"/>
-      <c r="C8" s="82" t="s">
+      <c r="D7" s="48"/>
+      <c r="E7" s="47"/>
+    </row>
+    <row r="8" ht="31" spans="1:5">
+      <c r="A8" s="44"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="64" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" ht="36" spans="1:3">
-      <c r="A9" s="79"/>
-      <c r="B9" s="80"/>
-      <c r="C9" s="86" t="s">
+      <c r="D8" s="47"/>
+      <c r="E8" s="47"/>
+    </row>
+    <row r="9" ht="31" spans="1:5">
+      <c r="A9" s="44"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="66" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" ht="18" spans="1:3">
-      <c r="A10" s="79"/>
-      <c r="B10" s="80"/>
-      <c r="C10" s="82" t="s">
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="44"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="64" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" ht="36" spans="1:3">
-      <c r="A11" s="79"/>
-      <c r="B11" s="80"/>
-      <c r="C11" s="82" t="s">
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+    </row>
+    <row r="11" ht="31" spans="1:5">
+      <c r="A11" s="44"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="64" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" ht="36" spans="1:3">
-      <c r="A12" s="79"/>
-      <c r="B12" s="80"/>
-      <c r="C12" s="82" t="s">
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+    </row>
+    <row r="12" ht="31" spans="1:5">
+      <c r="A12" s="44"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="64" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" ht="36" spans="1:3">
-      <c r="A13" s="79"/>
-      <c r="B13" s="80"/>
-      <c r="C13" s="82" t="s">
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+    </row>
+    <row r="13" ht="31" spans="1:5">
+      <c r="A13" s="44"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="64" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" ht="18" spans="1:3">
-      <c r="A14" s="79"/>
-      <c r="B14" s="80"/>
-      <c r="C14" s="82" t="s">
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="44"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="64" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" ht="18" spans="1:3">
-      <c r="A15" s="79"/>
-      <c r="B15" s="80"/>
-      <c r="C15" s="82" t="s">
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="44"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="64" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="16" ht="36" spans="1:3">
-      <c r="A16" s="79"/>
-      <c r="B16" s="80"/>
-      <c r="C16" s="87" t="s">
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+    </row>
+    <row r="16" ht="31" spans="1:5">
+      <c r="A16" s="44"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="61" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="17" ht="18" spans="1:3">
-      <c r="A17" s="79"/>
-      <c r="B17" s="80"/>
-      <c r="C17" s="82" t="s">
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="44"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="64" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" ht="18" spans="1:3">
-      <c r="A18" s="79"/>
-      <c r="B18" s="80"/>
-      <c r="C18" s="82" t="s">
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="44"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="64" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="19" ht="36" spans="1:3">
-      <c r="A19" s="79"/>
-      <c r="B19" s="80"/>
-      <c r="C19" s="82" t="s">
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+    </row>
+    <row r="19" ht="31" spans="1:5">
+      <c r="A19" s="44"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="64" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="20" ht="18" spans="1:3">
-      <c r="A20" s="79"/>
-      <c r="B20" s="80"/>
-      <c r="C20" s="82" t="s">
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="44"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="64" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="21" ht="36" spans="1:3">
-      <c r="A21" s="79"/>
-      <c r="B21" s="80"/>
-      <c r="C21" s="82" t="s">
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+    </row>
+    <row r="21" ht="31" spans="1:5">
+      <c r="A21" s="44"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="64" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" ht="18" spans="1:3">
-      <c r="A22" s="79"/>
-      <c r="B22" s="80"/>
-      <c r="C22" s="82" t="s">
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="44"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="64" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="23" ht="18" spans="1:3">
-      <c r="A23" s="79"/>
-      <c r="B23" s="80"/>
-      <c r="C23" s="82" t="s">
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="44"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="64" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="24" ht="18" spans="1:3">
-      <c r="A24" s="79"/>
-      <c r="B24" s="80"/>
-      <c r="C24" s="88" t="s">
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="44"/>
+      <c r="B24" s="33"/>
+      <c r="C24" s="65" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="25" ht="42" customHeight="1" spans="1:4">
-      <c r="A25" s="79"/>
-      <c r="B25" s="80"/>
-      <c r="C25" s="89" t="s">
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+    </row>
+    <row r="25" ht="31" spans="1:5">
+      <c r="A25" s="44"/>
+      <c r="B25" s="33"/>
+      <c r="C25" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="44"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="64" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="26" ht="18" spans="1:3">
-      <c r="A26" s="79"/>
-      <c r="B26" s="80"/>
-      <c r="C26" s="82" t="s">
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="44"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="64" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="27" ht="18" spans="1:3">
-      <c r="A27" s="79"/>
-      <c r="B27" s="80"/>
-      <c r="C27" s="82" t="s">
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="44"/>
+      <c r="B28" s="33"/>
+      <c r="C28" s="64" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="28" ht="18" spans="1:3">
-      <c r="A28" s="79"/>
-      <c r="B28" s="80"/>
-      <c r="C28" s="82" t="s">
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="44"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="64" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="29" ht="18" spans="1:3">
-      <c r="A29" s="79"/>
-      <c r="B29" s="80"/>
-      <c r="C29" s="82" t="s">
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="44"/>
+      <c r="B30" s="33"/>
+      <c r="C30" s="64" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="30" ht="18" spans="1:3">
-      <c r="A30" s="79"/>
-      <c r="B30" s="80"/>
-      <c r="C30" s="82" t="s">
+      <c r="D30" s="47"/>
+      <c r="E30" s="47"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="44"/>
+      <c r="B31" s="33"/>
+      <c r="C31" s="64" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="31" ht="18" spans="1:3">
-      <c r="A31" s="79"/>
-      <c r="B31" s="80"/>
-      <c r="C31" s="82" t="s">
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="44"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="64" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="32" ht="18" spans="1:3">
-      <c r="A32" s="79"/>
-      <c r="B32" s="80"/>
-      <c r="C32" s="82" t="s">
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="44"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="68" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="33" ht="18" spans="1:4">
-      <c r="A33" s="79"/>
-      <c r="B33" s="80"/>
-      <c r="C33" s="90" t="s">
+      <c r="D33" s="30"/>
+      <c r="E33" s="47"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="44"/>
+      <c r="B34" s="33"/>
+      <c r="C34" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="D33" s="77" t="s">
+      <c r="D34" s="31"/>
+      <c r="E34" s="47"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="44"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="68" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="34" ht="18" spans="1:4">
-      <c r="A34" s="79"/>
-      <c r="B34" s="80"/>
-      <c r="C34" s="91" t="s">
+      <c r="D35" s="31"/>
+      <c r="E35" s="47"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="44"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="D34" s="92"/>
-    </row>
-    <row r="35" ht="18" spans="1:4">
-      <c r="A35" s="79"/>
-      <c r="B35" s="80"/>
-      <c r="C35" s="90" t="s">
+      <c r="D36" s="31"/>
+      <c r="E36" s="47"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="44"/>
+      <c r="B37" s="33"/>
+      <c r="C37" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="D35" s="92"/>
-    </row>
-    <row r="36" ht="18" spans="1:4">
-      <c r="A36" s="79"/>
-      <c r="B36" s="80"/>
-      <c r="C36" s="91" t="s">
+      <c r="D37" s="31"/>
+      <c r="E37" s="47"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="44"/>
+      <c r="B38" s="33"/>
+      <c r="C38" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="D36" s="92"/>
-    </row>
-    <row r="37" ht="18" spans="1:4">
-      <c r="A37" s="79"/>
-      <c r="B37" s="80"/>
-      <c r="C37" s="91" t="s">
+      <c r="D38" s="31"/>
+      <c r="E38" s="47"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="44"/>
+      <c r="B39" s="33"/>
+      <c r="C39" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="D37" s="92"/>
-    </row>
-    <row r="38" ht="18" spans="1:4">
-      <c r="A38" s="79"/>
-      <c r="B38" s="80"/>
-      <c r="C38" s="91" t="s">
+      <c r="D39" s="31"/>
+      <c r="E39" s="47"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="44"/>
+      <c r="B40" s="33"/>
+      <c r="C40" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="D38" s="92"/>
-    </row>
-    <row r="39" ht="18" spans="1:4">
-      <c r="A39" s="79"/>
-      <c r="B39" s="80"/>
-      <c r="C39" s="91" t="s">
+      <c r="D40" s="31"/>
+      <c r="E40" s="47"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="44"/>
+      <c r="B41" s="33"/>
+      <c r="C41" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="D39" s="92"/>
-    </row>
-    <row r="40" ht="18" spans="1:4">
-      <c r="A40" s="79"/>
-      <c r="B40" s="80"/>
-      <c r="C40" s="91" t="s">
+      <c r="D41" s="31"/>
+      <c r="E41" s="47"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="44"/>
+      <c r="B42" s="33"/>
+      <c r="C42" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="D40" s="92"/>
-    </row>
-    <row r="41" ht="36" spans="1:4">
-      <c r="A41" s="79"/>
-      <c r="B41" s="80"/>
-      <c r="C41" s="91" t="s">
+      <c r="D42" s="47"/>
+      <c r="E42" s="47"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="44"/>
+      <c r="B43" s="33"/>
+      <c r="C43" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="D41" s="92"/>
-    </row>
-    <row r="42" ht="36" spans="1:3">
-      <c r="A42" s="79"/>
-      <c r="B42" s="80"/>
-      <c r="C42" s="82" t="s">
+      <c r="D43" s="47"/>
+      <c r="E43" s="47"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="44">
+        <v>2</v>
+      </c>
+      <c r="B44" s="33" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="43" ht="18" spans="1:3">
-      <c r="A43" s="79"/>
-      <c r="B43" s="80"/>
-      <c r="C43" s="82" t="s">
+      <c r="C44" s="61" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="44" ht="18" spans="1:3">
-      <c r="A44" s="79">
-        <v>2</v>
-      </c>
-      <c r="B44" s="81" t="s">
+      <c r="D44" s="47"/>
+      <c r="E44" s="47"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="44"/>
+      <c r="B45" s="33"/>
+      <c r="C45" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="C44" s="87" t="s">
+      <c r="D45" s="47"/>
+      <c r="E45" s="47"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="44"/>
+      <c r="B46" s="33"/>
+      <c r="C46" s="64" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="45" ht="18" spans="1:3">
-      <c r="A45" s="79"/>
-      <c r="B45" s="80"/>
-      <c r="C45" s="82" t="s">
+      <c r="D46" s="47"/>
+      <c r="E46" s="47"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="44"/>
+      <c r="B47" s="33"/>
+      <c r="C47" s="64" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="46" ht="18" spans="1:3">
-      <c r="A46" s="79"/>
-      <c r="B46" s="80"/>
-      <c r="C46" s="82" t="s">
+      <c r="D47" s="47"/>
+      <c r="E47" s="47"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="44"/>
+      <c r="B48" s="33"/>
+      <c r="C48" s="64" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="47" ht="18" spans="1:3">
-      <c r="A47" s="79"/>
-      <c r="B47" s="80"/>
-      <c r="C47" s="82" t="s">
+      <c r="D48" s="47"/>
+      <c r="E48" s="47"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="44"/>
+      <c r="B49" s="33"/>
+      <c r="C49" s="64" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="48" ht="18" spans="1:3">
-      <c r="A48" s="79"/>
-      <c r="B48" s="80"/>
-      <c r="C48" s="82" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="49" ht="18" spans="1:3">
-      <c r="A49" s="79"/>
-      <c r="B49" s="80"/>
-      <c r="C49" s="82" t="s">
-        <v>56</v>
-      </c>
+      <c r="D49" s="47"/>
+      <c r="E49" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -5051,543 +4570,583 @@
     <col min="3" max="3" width="17.4711538461538" style="29" customWidth="1"/>
     <col min="4" max="4" width="86.8557692307692" style="28" customWidth="1"/>
     <col min="5" max="5" width="12.8173076923077" style="29" customWidth="1"/>
-    <col min="6" max="6" width="68.7403846153846" style="63" customWidth="1"/>
+    <col min="6" max="6" width="68.7403846153846" style="57" customWidth="1"/>
     <col min="7" max="16384" width="9" style="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="96" customHeight="1" spans="1:6">
       <c r="A1" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="51"/>
+        <v>55</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="48"/>
     </row>
     <row r="2" ht="16" spans="1:6">
       <c r="A2" s="32" t="s">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="47" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="48" t="s">
-        <v>63</v>
+        <v>3</v>
+      </c>
+      <c r="E2" s="62" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="32" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3" ht="31" spans="1:6">
       <c r="A3" s="33"/>
       <c r="B3" s="33"/>
-      <c r="C3" s="66" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="67" t="s">
-        <v>65</v>
-      </c>
-      <c r="E3" s="76"/>
-      <c r="F3" s="51"/>
+      <c r="C3" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="63"/>
+      <c r="F3" s="48"/>
     </row>
     <row r="4" ht="46" spans="1:6">
       <c r="A4" s="33"/>
       <c r="B4" s="33"/>
-      <c r="C4" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" s="67" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4" s="51" t="s">
-        <v>69</v>
+      <c r="C4" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="59" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="48" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="5" ht="46" spans="1:6">
       <c r="A5" s="33"/>
       <c r="B5" s="33"/>
-      <c r="C5" s="68" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="67" t="s">
-        <v>71</v>
-      </c>
-      <c r="E5" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="51" t="s">
-        <v>69</v>
+      <c r="C5" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="59" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" s="48" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="6" ht="16" spans="1:6">
       <c r="A6" s="33"/>
       <c r="B6" s="33"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="67" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="51"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="48"/>
     </row>
     <row r="7" ht="16" spans="1:6">
       <c r="A7" s="33"/>
       <c r="B7" s="33"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="67" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="76"/>
-      <c r="F7" s="51"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="59" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="63"/>
+      <c r="F7" s="48"/>
     </row>
     <row r="8" ht="16" spans="1:6">
       <c r="A8" s="33"/>
       <c r="B8" s="33"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="67" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" s="51"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="59" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="48"/>
     </row>
     <row r="9" ht="16" spans="1:6">
       <c r="A9" s="33"/>
       <c r="B9" s="33"/>
-      <c r="C9" s="68" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="67" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" s="49" t="s">
+      <c r="C9" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="F9" s="51"/>
+      <c r="D9" s="59" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" s="48"/>
     </row>
     <row r="10" ht="16" spans="1:6">
       <c r="A10" s="33"/>
       <c r="B10" s="33"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="67" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F10" s="51"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="59" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="48"/>
     </row>
     <row r="11" ht="16" spans="1:6">
       <c r="A11" s="33"/>
       <c r="B11" s="33"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="67" t="s">
-        <v>73</v>
-      </c>
-      <c r="E11" s="76"/>
-      <c r="F11" s="51"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="59" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="63"/>
+      <c r="F11" s="48"/>
     </row>
     <row r="12" ht="16" spans="1:6">
       <c r="A12" s="33"/>
       <c r="B12" s="33"/>
-      <c r="C12" s="70"/>
-      <c r="D12" s="67" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F12" s="51"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="59" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="48"/>
     </row>
     <row r="13" ht="46" spans="1:6">
       <c r="A13" s="33"/>
       <c r="B13" s="33"/>
-      <c r="C13" s="68" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="67" t="s">
-        <v>79</v>
-      </c>
-      <c r="E13" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" s="51" t="s">
-        <v>69</v>
+      <c r="C13" s="41" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="59" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="48" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="14" ht="16" spans="1:6">
       <c r="A14" s="33"/>
       <c r="B14" s="33"/>
-      <c r="C14" s="69"/>
-      <c r="D14" s="67" t="s">
-        <v>80</v>
-      </c>
-      <c r="E14" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" s="51"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="59" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="48"/>
     </row>
     <row r="15" ht="31" spans="1:6">
       <c r="A15" s="33"/>
       <c r="B15" s="33"/>
-      <c r="C15" s="70"/>
-      <c r="D15" s="67" t="s">
-        <v>81</v>
-      </c>
-      <c r="E15" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" s="51"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="59" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="48"/>
     </row>
     <row r="16" ht="46" spans="1:6">
       <c r="A16" s="33"/>
       <c r="B16" s="33"/>
-      <c r="C16" s="68" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" s="67" t="s">
-        <v>83</v>
-      </c>
-      <c r="E16" s="49"/>
-      <c r="F16" s="51"/>
+      <c r="C16" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="59" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" s="48"/>
     </row>
     <row r="17" ht="46" spans="1:6">
       <c r="A17" s="33"/>
       <c r="B17" s="33"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="67" t="s">
-        <v>84</v>
-      </c>
-      <c r="E17" s="49"/>
-      <c r="F17" s="51"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="48"/>
     </row>
     <row r="18" ht="61" spans="1:6">
       <c r="A18" s="33"/>
       <c r="B18" s="33"/>
-      <c r="C18" s="69"/>
-      <c r="D18" s="71" t="s">
-        <v>85</v>
-      </c>
-      <c r="E18" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F18" s="51" t="s">
-        <v>86</v>
+      <c r="C18" s="42"/>
+      <c r="D18" s="60" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F18" s="48" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="19" ht="16" spans="1:6">
       <c r="A19" s="33"/>
       <c r="B19" s="33"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="67" t="s">
-        <v>87</v>
-      </c>
-      <c r="E19" s="49"/>
-      <c r="F19" s="51"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="59" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" s="48"/>
     </row>
     <row r="20" ht="16" spans="1:6">
       <c r="A20" s="33"/>
       <c r="B20" s="33"/>
-      <c r="C20" s="70"/>
-      <c r="D20" s="67" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20" s="49"/>
-      <c r="F20" s="51"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="59" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="63" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" s="48"/>
     </row>
     <row r="21" ht="31" spans="1:6">
       <c r="A21" s="33"/>
       <c r="B21" s="33"/>
-      <c r="C21" s="66" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21" s="67" t="s">
-        <v>90</v>
-      </c>
-      <c r="E21" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="F21" s="51" t="s">
-        <v>92</v>
+      <c r="C21" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" s="59" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" s="63" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21" s="48" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="22" ht="76" spans="1:6">
       <c r="A22" s="33"/>
       <c r="B22" s="33"/>
-      <c r="C22" s="72" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" s="67" t="s">
-        <v>94</v>
-      </c>
-      <c r="E22" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="F22" s="51" t="s">
-        <v>95</v>
+      <c r="C22" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="59" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="63" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" s="48" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="23" ht="16" spans="1:6">
       <c r="A23" s="33"/>
       <c r="B23" s="33"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="67" t="s">
-        <v>96</v>
-      </c>
-      <c r="E23" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F23" s="51"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="59" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" s="48"/>
     </row>
     <row r="24" ht="16" spans="1:6">
       <c r="A24" s="33"/>
       <c r="B24" s="33"/>
-      <c r="C24" s="74"/>
-      <c r="D24" s="67" t="s">
-        <v>97</v>
-      </c>
-      <c r="E24" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F24" s="51"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="48"/>
     </row>
     <row r="25" ht="31" spans="1:6">
       <c r="A25" s="33"/>
       <c r="B25" s="33"/>
-      <c r="C25" s="68" t="s">
-        <v>98</v>
-      </c>
-      <c r="D25" s="67" t="s">
-        <v>99</v>
-      </c>
-      <c r="E25" s="49"/>
-      <c r="F25" s="51"/>
+      <c r="C25" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E25" s="44"/>
+      <c r="F25" s="48" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="26" ht="31" spans="1:6">
       <c r="A26" s="33"/>
       <c r="B26" s="33"/>
-      <c r="C26" s="69"/>
-      <c r="D26" s="67" t="s">
-        <v>100</v>
-      </c>
-      <c r="E26" s="49"/>
-      <c r="F26" s="51"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F26" s="48"/>
     </row>
     <row r="27" ht="31" spans="1:6">
       <c r="A27" s="33"/>
       <c r="B27" s="33"/>
-      <c r="C27" s="69"/>
-      <c r="D27" s="67" t="s">
-        <v>101</v>
-      </c>
-      <c r="E27" s="49"/>
-      <c r="F27" s="51"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" s="48" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="28" ht="31" spans="1:6">
       <c r="A28" s="33"/>
       <c r="B28" s="33"/>
-      <c r="C28" s="69"/>
-      <c r="D28" s="67" t="s">
-        <v>102</v>
-      </c>
-      <c r="E28" s="49"/>
-      <c r="F28" s="51"/>
+      <c r="C28" s="42"/>
+      <c r="D28" s="59" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="44"/>
+      <c r="F28" s="48"/>
     </row>
     <row r="29" ht="16" spans="1:6">
       <c r="A29" s="33"/>
       <c r="B29" s="33"/>
-      <c r="C29" s="69"/>
-      <c r="D29" s="67" t="s">
-        <v>88</v>
-      </c>
-      <c r="E29" s="49"/>
-      <c r="F29" s="51"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="59" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" s="44"/>
+      <c r="F29" s="48"/>
     </row>
     <row r="30" ht="16" spans="1:6">
       <c r="A30" s="33"/>
       <c r="B30" s="33"/>
-      <c r="C30" s="69"/>
-      <c r="D30" s="67" t="s">
-        <v>103</v>
-      </c>
-      <c r="E30" s="49"/>
-      <c r="F30" s="51"/>
+      <c r="C30" s="42"/>
+      <c r="D30" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="E30" s="44"/>
+      <c r="F30" s="48"/>
     </row>
     <row r="31" ht="31" spans="1:6">
       <c r="A31" s="33"/>
       <c r="B31" s="33"/>
-      <c r="C31" s="70"/>
-      <c r="D31" s="67" t="s">
-        <v>104</v>
-      </c>
-      <c r="E31" s="49"/>
-      <c r="F31" s="51"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="59" t="s">
+        <v>100</v>
+      </c>
+      <c r="E31" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="F31" s="48"/>
     </row>
     <row r="32" ht="31" spans="1:6">
       <c r="A32" s="33"/>
       <c r="B32" s="33"/>
-      <c r="C32" s="68" t="s">
-        <v>105</v>
-      </c>
-      <c r="D32" s="67" t="s">
-        <v>106</v>
-      </c>
-      <c r="E32" s="49"/>
-      <c r="F32" s="51"/>
+      <c r="C32" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="D32" s="59" t="s">
+        <v>102</v>
+      </c>
+      <c r="E32" s="44"/>
+      <c r="F32" s="48"/>
     </row>
     <row r="33" ht="16" spans="1:6">
       <c r="A33" s="33"/>
       <c r="B33" s="33"/>
-      <c r="C33" s="69"/>
-      <c r="D33" s="67" t="s">
-        <v>107</v>
-      </c>
-      <c r="E33" s="49"/>
-      <c r="F33" s="51"/>
+      <c r="C33" s="42"/>
+      <c r="D33" s="59" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F33" s="48"/>
     </row>
     <row r="34" ht="16" spans="1:6">
       <c r="A34" s="33"/>
       <c r="B34" s="33"/>
-      <c r="C34" s="69"/>
-      <c r="D34" s="67" t="s">
-        <v>108</v>
-      </c>
-      <c r="E34" s="49"/>
-      <c r="F34" s="51"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="E34" s="44"/>
+      <c r="F34" s="48"/>
     </row>
     <row r="35" ht="31" spans="1:6">
       <c r="A35" s="33"/>
       <c r="B35" s="33"/>
-      <c r="C35" s="69"/>
-      <c r="D35" s="67" t="s">
-        <v>109</v>
-      </c>
-      <c r="E35" s="49"/>
-      <c r="F35" s="51"/>
+      <c r="C35" s="42"/>
+      <c r="D35" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="E35" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="F35" s="48"/>
     </row>
     <row r="36" ht="31" spans="1:6">
       <c r="A36" s="33"/>
       <c r="B36" s="33"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="67" t="s">
-        <v>110</v>
-      </c>
-      <c r="E36" s="49"/>
-      <c r="F36" s="51"/>
+      <c r="C36" s="42"/>
+      <c r="D36" s="59" t="s">
+        <v>106</v>
+      </c>
+      <c r="E36" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="F36" s="48"/>
     </row>
     <row r="37" ht="31" spans="1:6">
       <c r="A37" s="33"/>
       <c r="B37" s="33"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="67" t="s">
-        <v>111</v>
-      </c>
-      <c r="E37" s="49"/>
-      <c r="F37" s="51"/>
+      <c r="C37" s="42"/>
+      <c r="D37" s="59" t="s">
+        <v>107</v>
+      </c>
+      <c r="E37" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="F37" s="48"/>
     </row>
     <row r="38" ht="31" spans="1:6">
       <c r="A38" s="33"/>
       <c r="B38" s="33"/>
-      <c r="C38" s="70"/>
-      <c r="D38" s="67" t="s">
-        <v>112</v>
-      </c>
-      <c r="E38" s="49"/>
-      <c r="F38" s="51"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="E38" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="F38" s="48"/>
     </row>
     <row r="39" ht="46" spans="1:6">
       <c r="A39" s="33"/>
       <c r="B39" s="33"/>
-      <c r="C39" s="68" t="s">
-        <v>113</v>
-      </c>
-      <c r="D39" s="67" t="s">
-        <v>114</v>
-      </c>
-      <c r="E39" s="49"/>
-      <c r="F39" s="51"/>
+      <c r="C39" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="D39" s="59" t="s">
+        <v>110</v>
+      </c>
+      <c r="E39" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F39" s="48"/>
     </row>
     <row r="40" ht="31" spans="1:6">
       <c r="A40" s="33"/>
       <c r="B40" s="33"/>
-      <c r="C40" s="69"/>
-      <c r="D40" s="67" t="s">
-        <v>115</v>
-      </c>
-      <c r="E40" s="49"/>
-      <c r="F40" s="51"/>
+      <c r="C40" s="42"/>
+      <c r="D40" s="59" t="s">
+        <v>111</v>
+      </c>
+      <c r="E40" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F40" s="48"/>
     </row>
     <row r="41" ht="46" spans="1:6">
       <c r="A41" s="33"/>
       <c r="B41" s="33"/>
-      <c r="C41" s="69"/>
-      <c r="D41" s="67" t="s">
-        <v>116</v>
-      </c>
-      <c r="E41" s="49"/>
-      <c r="F41" s="51"/>
+      <c r="C41" s="42"/>
+      <c r="D41" s="59" t="s">
+        <v>112</v>
+      </c>
+      <c r="E41" s="44"/>
+      <c r="F41" s="48"/>
     </row>
     <row r="42" ht="46" spans="1:6">
       <c r="A42" s="33"/>
       <c r="B42" s="33"/>
-      <c r="C42" s="69"/>
-      <c r="D42" s="67" t="s">
-        <v>117</v>
-      </c>
-      <c r="E42" s="53"/>
-      <c r="F42" s="51"/>
+      <c r="C42" s="42"/>
+      <c r="D42" s="59" t="s">
+        <v>113</v>
+      </c>
+      <c r="E42" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="F42" s="48" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="43" ht="46" spans="1:6">
       <c r="A43" s="33"/>
       <c r="B43" s="33"/>
-      <c r="C43" s="69"/>
-      <c r="D43" s="67" t="s">
-        <v>118</v>
-      </c>
-      <c r="E43" s="49"/>
-      <c r="F43" s="51"/>
+      <c r="C43" s="42"/>
+      <c r="D43" s="59" t="s">
+        <v>115</v>
+      </c>
+      <c r="E43" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="F43" s="48"/>
     </row>
     <row r="44" ht="46" spans="1:6">
       <c r="A44" s="33"/>
       <c r="B44" s="33"/>
-      <c r="C44" s="69"/>
-      <c r="D44" s="67" t="s">
-        <v>119</v>
-      </c>
-      <c r="E44" s="49"/>
-      <c r="F44" s="51"/>
+      <c r="C44" s="42"/>
+      <c r="D44" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="E44" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="F44" s="48"/>
     </row>
     <row r="45" ht="46" spans="1:6">
       <c r="A45" s="33"/>
       <c r="B45" s="33"/>
-      <c r="C45" s="69"/>
-      <c r="D45" s="67" t="s">
-        <v>120</v>
-      </c>
-      <c r="E45" s="49"/>
-      <c r="F45" s="51"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="E45" s="44"/>
+      <c r="F45" s="48"/>
     </row>
     <row r="46" ht="16" spans="1:6">
       <c r="A46" s="33"/>
       <c r="B46" s="33"/>
-      <c r="C46" s="70"/>
-      <c r="D46" s="75" t="s">
-        <v>121</v>
-      </c>
-      <c r="E46" s="49"/>
-      <c r="F46" s="51"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="E46" s="44"/>
+      <c r="F46" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -5625,32 +5184,32 @@
   <sheetData>
     <row r="1" s="27" customFormat="1" ht="30" customHeight="1" spans="1:6">
       <c r="A1" s="30" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="31"/>
     </row>
     <row r="2" ht="16" spans="1:6">
       <c r="A2" s="32" t="s">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="47" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="48" t="s">
-        <v>63</v>
+        <v>3</v>
+      </c>
+      <c r="E2" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="46" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3" ht="16" spans="1:6">
@@ -5658,1330 +5217,1338 @@
         <v>1</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="E3" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F3" s="50"/>
+        <v>122</v>
+      </c>
+      <c r="E3" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="47"/>
     </row>
     <row r="4" ht="31" spans="1:6">
       <c r="A4" s="33"/>
       <c r="B4" s="33"/>
       <c r="C4" s="35"/>
       <c r="D4" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="E4" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4" s="50"/>
+        <v>123</v>
+      </c>
+      <c r="E4" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="47"/>
     </row>
     <row r="5" ht="31" spans="1:6">
       <c r="A5" s="33"/>
       <c r="B5" s="33"/>
       <c r="C5" s="35"/>
       <c r="D5" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="50"/>
+        <v>124</v>
+      </c>
+      <c r="E5" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" s="47"/>
     </row>
     <row r="6" ht="16" spans="1:6">
       <c r="A6" s="33"/>
       <c r="B6" s="33"/>
       <c r="C6" s="37"/>
-      <c r="D6" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="E6" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="50"/>
+      <c r="D6" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="E6" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="47"/>
     </row>
     <row r="7" ht="61" spans="1:6">
       <c r="A7" s="33"/>
       <c r="B7" s="33"/>
-      <c r="C7" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="D7" s="38" t="s">
-        <v>130</v>
-      </c>
-      <c r="E7" s="49"/>
-      <c r="F7" s="51" t="s">
-        <v>131</v>
+      <c r="C7" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="E7" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" s="48" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="8" ht="16" spans="1:6">
       <c r="A8" s="33"/>
       <c r="B8" s="33"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="38" t="s">
-        <v>132</v>
-      </c>
-      <c r="E8" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" s="50"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="47"/>
     </row>
     <row r="9" ht="46" spans="1:6">
       <c r="A9" s="33"/>
       <c r="B9" s="33"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="E9" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="F9" s="52" t="s">
-        <v>135</v>
+      <c r="C9" s="39"/>
+      <c r="D9" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="E9" s="44" t="s">
+        <v>131</v>
+      </c>
+      <c r="F9" s="48" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="10" ht="52" customHeight="1" spans="1:6">
       <c r="A10" s="33"/>
       <c r="B10" s="33"/>
-      <c r="C10" s="41"/>
+      <c r="C10" s="40"/>
       <c r="D10" s="36" t="s">
-        <v>136</v>
-      </c>
-      <c r="E10" s="53" t="s">
-        <v>91</v>
-      </c>
-      <c r="F10" s="51" t="s">
-        <v>137</v>
+        <v>133</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="48" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="11" ht="16" spans="1:6">
       <c r="A11" s="33"/>
       <c r="B11" s="33"/>
-      <c r="C11" s="39" t="s">
-        <v>138</v>
-      </c>
-      <c r="D11" s="38" t="s">
-        <v>139</v>
-      </c>
-      <c r="E11" s="49"/>
-      <c r="F11" s="50"/>
+      <c r="C11" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="47"/>
     </row>
     <row r="12" ht="16" spans="1:6">
       <c r="A12" s="33"/>
       <c r="B12" s="33"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="38" t="s">
-        <v>140</v>
-      </c>
-      <c r="E12" s="49"/>
-      <c r="F12" s="50"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="E12" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="47"/>
     </row>
     <row r="13" ht="31" spans="1:6">
       <c r="A13" s="33"/>
       <c r="B13" s="33"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="38" t="s">
-        <v>141</v>
-      </c>
-      <c r="E13" s="49"/>
-      <c r="F13" s="50"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="36" t="s">
+        <v>138</v>
+      </c>
+      <c r="E13" s="44"/>
+      <c r="F13" s="47"/>
     </row>
     <row r="14" ht="16" spans="1:6">
       <c r="A14" s="33"/>
       <c r="B14" s="33"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="38" t="s">
-        <v>142</v>
-      </c>
-      <c r="E14" s="49"/>
-      <c r="F14" s="50"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="E14" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="47"/>
     </row>
     <row r="15" ht="16" spans="1:6">
       <c r="A15" s="33"/>
       <c r="B15" s="33"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="E15" s="49"/>
-      <c r="F15" s="50"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="E15" s="44"/>
+      <c r="F15" s="47"/>
     </row>
     <row r="16" ht="107" spans="1:6">
       <c r="A16" s="33"/>
       <c r="B16" s="33"/>
-      <c r="C16" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="D16" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="E16" s="49"/>
-      <c r="F16" s="51" t="s">
-        <v>146</v>
+      <c r="C16" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="E16" s="44"/>
+      <c r="F16" s="48" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="17" ht="16" spans="1:6">
       <c r="A17" s="33"/>
       <c r="B17" s="33"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="38" t="s">
-        <v>147</v>
-      </c>
-      <c r="E17" s="49"/>
-      <c r="F17" s="50"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="E17" s="44"/>
+      <c r="F17" s="47"/>
     </row>
     <row r="18" ht="16" spans="1:6">
       <c r="A18" s="33"/>
       <c r="B18" s="33"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="E18" s="49"/>
-      <c r="F18" s="50" t="s">
-        <v>149</v>
+      <c r="C18" s="39"/>
+      <c r="D18" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="E18" s="44"/>
+      <c r="F18" s="47" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="19" ht="46" spans="1:6">
       <c r="A19" s="33"/>
       <c r="B19" s="33"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="38" t="s">
-        <v>150</v>
-      </c>
-      <c r="E19" s="49"/>
-      <c r="F19" s="51" t="s">
-        <v>151</v>
+      <c r="C19" s="39"/>
+      <c r="D19" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="E19" s="44"/>
+      <c r="F19" s="48" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="20" ht="31" spans="1:6">
       <c r="A20" s="33"/>
       <c r="B20" s="33"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="38" t="s">
-        <v>152</v>
-      </c>
-      <c r="E20" s="49"/>
-      <c r="F20" s="51" t="s">
-        <v>153</v>
+      <c r="C20" s="39"/>
+      <c r="D20" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="E20" s="44"/>
+      <c r="F20" s="48" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="21" ht="16" spans="1:6">
       <c r="A21" s="33"/>
       <c r="B21" s="33"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="38" t="s">
-        <v>154</v>
-      </c>
-      <c r="E21" s="49"/>
-      <c r="F21" s="50"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="E21" s="44"/>
+      <c r="F21" s="47"/>
     </row>
     <row r="22" ht="16" spans="1:6">
       <c r="A22" s="33"/>
       <c r="B22" s="33"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="38" t="s">
-        <v>155</v>
-      </c>
-      <c r="E22" s="49"/>
-      <c r="F22" s="50" t="s">
-        <v>156</v>
+      <c r="C22" s="39"/>
+      <c r="D22" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="E22" s="44"/>
+      <c r="F22" s="47" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="23" ht="16" spans="1:6">
       <c r="A23" s="33"/>
       <c r="B23" s="33"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="38" t="s">
-        <v>157</v>
-      </c>
-      <c r="E23" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F23" s="50" t="s">
-        <v>158</v>
+      <c r="C23" s="39"/>
+      <c r="D23" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="E23" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" s="47" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="24" ht="16" spans="1:6">
       <c r="A24" s="33"/>
       <c r="B24" s="33"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="E24" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F24" s="50" t="s">
-        <v>158</v>
+      <c r="C24" s="39"/>
+      <c r="D24" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="E24" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="47" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="25" ht="31" spans="1:6">
       <c r="A25" s="33"/>
       <c r="B25" s="33"/>
-      <c r="C25" s="40"/>
+      <c r="C25" s="39"/>
       <c r="D25" s="36" t="s">
-        <v>160</v>
-      </c>
-      <c r="E25" s="54"/>
-      <c r="F25" s="50"/>
+        <v>157</v>
+      </c>
+      <c r="E25" s="33"/>
+      <c r="F25" s="47"/>
     </row>
     <row r="26" ht="31" spans="1:6">
       <c r="A26" s="33"/>
       <c r="B26" s="33"/>
-      <c r="C26" s="41"/>
+      <c r="C26" s="40"/>
       <c r="D26" s="36" t="s">
-        <v>161</v>
-      </c>
-      <c r="E26" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F26" s="50"/>
+        <v>158</v>
+      </c>
+      <c r="E26" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F26" s="47"/>
     </row>
     <row r="27" ht="107" spans="1:6">
       <c r="A27" s="33"/>
       <c r="B27" s="33"/>
-      <c r="C27" s="42" t="s">
-        <v>162</v>
-      </c>
-      <c r="D27" s="38" t="s">
-        <v>163</v>
-      </c>
-      <c r="E27" s="49"/>
-      <c r="F27" s="51" t="s">
-        <v>164</v>
+      <c r="C27" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="D27" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="E27" s="44"/>
+      <c r="F27" s="48" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="28" ht="16" spans="1:6">
       <c r="A28" s="33"/>
       <c r="B28" s="33"/>
-      <c r="C28" s="43"/>
-      <c r="D28" s="38" t="s">
-        <v>165</v>
-      </c>
-      <c r="E28" s="49"/>
-      <c r="F28" s="50" t="s">
-        <v>149</v>
+      <c r="C28" s="42"/>
+      <c r="D28" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E28" s="44"/>
+      <c r="F28" s="47" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="29" ht="46" spans="1:6">
       <c r="A29" s="33"/>
       <c r="B29" s="33"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="38" t="s">
-        <v>166</v>
-      </c>
-      <c r="E29" s="49"/>
-      <c r="F29" s="51" t="s">
-        <v>167</v>
+      <c r="C29" s="42"/>
+      <c r="D29" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="E29" s="44"/>
+      <c r="F29" s="48" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="30" ht="43" customHeight="1" spans="1:6">
       <c r="A30" s="33"/>
       <c r="B30" s="33"/>
-      <c r="C30" s="43"/>
+      <c r="C30" s="42"/>
       <c r="D30" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="E30" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F30" s="50" t="s">
-        <v>169</v>
+        <v>165</v>
+      </c>
+      <c r="E30" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F30" s="47" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="31" ht="16" spans="1:6">
       <c r="A31" s="33"/>
       <c r="B31" s="33"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="E31" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F31" s="50" t="s">
-        <v>171</v>
+      <c r="C31" s="42"/>
+      <c r="D31" s="36" t="s">
+        <v>167</v>
+      </c>
+      <c r="E31" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F31" s="47" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="32" ht="16" spans="1:6">
       <c r="A32" s="33"/>
       <c r="B32" s="33"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="38" t="s">
-        <v>172</v>
-      </c>
-      <c r="E32" s="49"/>
-      <c r="F32" s="55" t="s">
-        <v>173</v>
+      <c r="C32" s="42"/>
+      <c r="D32" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="E32" s="44"/>
+      <c r="F32" s="49" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="33" ht="61" spans="1:6">
       <c r="A33" s="33"/>
       <c r="B33" s="33"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="38" t="s">
-        <v>174</v>
-      </c>
-      <c r="E33" s="49"/>
-      <c r="F33" s="52" t="s">
-        <v>175</v>
+      <c r="C33" s="42"/>
+      <c r="D33" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="E33" s="44"/>
+      <c r="F33" s="48" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="34" ht="31" spans="1:6">
       <c r="A34" s="33"/>
       <c r="B34" s="33"/>
-      <c r="C34" s="43"/>
-      <c r="D34" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="E34" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F34" s="50" t="s">
-        <v>162</v>
+      <c r="C34" s="42"/>
+      <c r="D34" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="E34" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F34" s="47" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="35" ht="16" spans="1:6">
       <c r="A35" s="33"/>
       <c r="B35" s="33"/>
-      <c r="C35" s="43"/>
-      <c r="D35" s="38" t="s">
-        <v>177</v>
-      </c>
-      <c r="E35" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F35" s="50" t="s">
-        <v>162</v>
+      <c r="C35" s="42"/>
+      <c r="D35" s="36" t="s">
+        <v>174</v>
+      </c>
+      <c r="E35" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F35" s="47" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="36" ht="16" spans="1:6">
       <c r="A36" s="33"/>
       <c r="B36" s="33"/>
-      <c r="C36" s="43"/>
-      <c r="D36" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="E36" s="49"/>
-      <c r="F36" s="55" t="s">
-        <v>173</v>
+      <c r="C36" s="42"/>
+      <c r="D36" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="E36" s="44"/>
+      <c r="F36" s="49" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="37" ht="52" customHeight="1" spans="1:6">
       <c r="A37" s="33"/>
       <c r="B37" s="33"/>
-      <c r="C37" s="43"/>
+      <c r="C37" s="42"/>
       <c r="D37" s="36" t="s">
-        <v>179</v>
-      </c>
-      <c r="E37" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F37" s="50"/>
+        <v>176</v>
+      </c>
+      <c r="E37" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F37" s="47"/>
     </row>
     <row r="38" ht="16" spans="1:6">
       <c r="A38" s="33"/>
       <c r="B38" s="33"/>
-      <c r="C38" s="43"/>
-      <c r="D38" s="38" t="s">
-        <v>180</v>
-      </c>
-      <c r="E38" s="49"/>
-      <c r="F38" s="50" t="s">
-        <v>181</v>
+      <c r="C38" s="42"/>
+      <c r="D38" s="36" t="s">
+        <v>177</v>
+      </c>
+      <c r="E38" s="44"/>
+      <c r="F38" s="47" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="39" ht="16" spans="1:6">
       <c r="A39" s="33"/>
       <c r="B39" s="33"/>
-      <c r="C39" s="43"/>
-      <c r="D39" s="38" t="s">
-        <v>182</v>
-      </c>
-      <c r="E39" s="49"/>
-      <c r="F39" s="50" t="s">
-        <v>183</v>
+      <c r="C39" s="42"/>
+      <c r="D39" s="36" t="s">
+        <v>179</v>
+      </c>
+      <c r="E39" s="44"/>
+      <c r="F39" s="47" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="40" ht="31" spans="1:6">
       <c r="A40" s="33"/>
       <c r="B40" s="33"/>
-      <c r="C40" s="43"/>
-      <c r="D40" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="E40" s="49"/>
-      <c r="F40" s="50"/>
+      <c r="C40" s="42"/>
+      <c r="D40" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="E40" s="44"/>
+      <c r="F40" s="47"/>
     </row>
     <row r="41" ht="16" spans="1:6">
       <c r="A41" s="33"/>
       <c r="B41" s="33"/>
-      <c r="C41" s="43"/>
-      <c r="D41" s="38" t="s">
-        <v>185</v>
-      </c>
-      <c r="E41" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F41" s="50" t="s">
-        <v>186</v>
+      <c r="C41" s="42"/>
+      <c r="D41" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="E41" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F41" s="47" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="42" ht="16" spans="1:6">
       <c r="A42" s="33"/>
       <c r="B42" s="33"/>
-      <c r="C42" s="44"/>
-      <c r="D42" s="38" t="s">
-        <v>187</v>
-      </c>
-      <c r="E42" s="49"/>
-      <c r="F42" s="50" t="s">
-        <v>188</v>
+      <c r="C42" s="43"/>
+      <c r="D42" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="E42" s="44"/>
+      <c r="F42" s="47" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="43" ht="46" spans="1:6">
       <c r="A43" s="33"/>
       <c r="B43" s="33"/>
-      <c r="C43" s="42" t="s">
-        <v>189</v>
-      </c>
-      <c r="D43" s="38" t="s">
-        <v>190</v>
-      </c>
-      <c r="E43" s="49"/>
-      <c r="F43" s="51" t="s">
-        <v>191</v>
+      <c r="C43" s="41" t="s">
+        <v>186</v>
+      </c>
+      <c r="D43" s="36" t="s">
+        <v>187</v>
+      </c>
+      <c r="E43" s="44"/>
+      <c r="F43" s="48" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="44" ht="31" spans="1:6">
       <c r="A44" s="33"/>
       <c r="B44" s="33"/>
-      <c r="C44" s="43"/>
-      <c r="D44" s="38" t="s">
-        <v>192</v>
-      </c>
-      <c r="E44" s="49"/>
-      <c r="F44" s="51" t="s">
-        <v>193</v>
+      <c r="C44" s="42"/>
+      <c r="D44" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="44"/>
+      <c r="F44" s="48" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="45" ht="31" spans="1:6">
       <c r="A45" s="33"/>
       <c r="B45" s="33"/>
-      <c r="C45" s="43"/>
-      <c r="D45" s="38" t="s">
-        <v>194</v>
-      </c>
-      <c r="E45" s="49"/>
-      <c r="F45" s="50"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="E45" s="44"/>
+      <c r="F45" s="47"/>
     </row>
     <row r="46" ht="31" spans="1:6">
       <c r="A46" s="33"/>
       <c r="B46" s="33"/>
-      <c r="C46" s="43"/>
-      <c r="D46" s="38" t="s">
-        <v>195</v>
-      </c>
-      <c r="E46" s="49"/>
-      <c r="F46" s="50"/>
+      <c r="C46" s="42"/>
+      <c r="D46" s="36" t="s">
+        <v>192</v>
+      </c>
+      <c r="E46" s="44"/>
+      <c r="F46" s="47"/>
     </row>
     <row r="47" ht="16" spans="1:6">
       <c r="A47" s="33"/>
       <c r="B47" s="33"/>
-      <c r="C47" s="43"/>
-      <c r="D47" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="E47" s="49"/>
-      <c r="F47" s="50" t="s">
-        <v>197</v>
+      <c r="C47" s="42"/>
+      <c r="D47" s="36" t="s">
+        <v>193</v>
+      </c>
+      <c r="E47" s="44"/>
+      <c r="F47" s="47" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="48" ht="16" spans="1:6">
       <c r="A48" s="33"/>
       <c r="B48" s="33"/>
-      <c r="C48" s="43"/>
-      <c r="D48" s="38" t="s">
-        <v>198</v>
-      </c>
-      <c r="E48" s="49"/>
-      <c r="F48" s="50"/>
+      <c r="C48" s="42"/>
+      <c r="D48" s="36" t="s">
+        <v>195</v>
+      </c>
+      <c r="E48" s="44"/>
+      <c r="F48" s="47"/>
     </row>
     <row r="49" ht="16" spans="1:6">
       <c r="A49" s="33"/>
       <c r="B49" s="33"/>
-      <c r="C49" s="43"/>
-      <c r="D49" s="38" t="s">
-        <v>199</v>
-      </c>
-      <c r="E49" s="49"/>
-      <c r="F49" s="50"/>
+      <c r="C49" s="42"/>
+      <c r="D49" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="E49" s="44"/>
+      <c r="F49" s="47"/>
     </row>
     <row r="50" ht="16" spans="1:6">
       <c r="A50" s="33"/>
       <c r="B50" s="33"/>
-      <c r="C50" s="43"/>
-      <c r="D50" s="38" t="s">
-        <v>200</v>
-      </c>
-      <c r="E50" s="49"/>
-      <c r="F50" s="50"/>
+      <c r="C50" s="42"/>
+      <c r="D50" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="E50" s="44"/>
+      <c r="F50" s="47"/>
     </row>
     <row r="51" ht="16" spans="1:6">
       <c r="A51" s="33"/>
       <c r="B51" s="33"/>
-      <c r="C51" s="44"/>
-      <c r="D51" s="38" t="s">
-        <v>201</v>
-      </c>
-      <c r="E51" s="49"/>
-      <c r="F51" s="50"/>
+      <c r="C51" s="43"/>
+      <c r="D51" s="36" t="s">
+        <v>198</v>
+      </c>
+      <c r="E51" s="44"/>
+      <c r="F51" s="47"/>
     </row>
     <row r="52" ht="61" spans="1:6">
       <c r="A52" s="33"/>
       <c r="B52" s="33"/>
-      <c r="C52" s="39" t="s">
-        <v>202</v>
-      </c>
-      <c r="D52" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="E52" s="49"/>
-      <c r="F52" s="51" t="s">
-        <v>204</v>
+      <c r="C52" s="38" t="s">
+        <v>199</v>
+      </c>
+      <c r="D52" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="E52" s="44"/>
+      <c r="F52" s="48" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="53" ht="16" spans="1:6">
       <c r="A53" s="33"/>
       <c r="B53" s="33"/>
-      <c r="C53" s="40"/>
-      <c r="D53" s="38" t="s">
-        <v>205</v>
-      </c>
-      <c r="E53" s="49"/>
-      <c r="F53" s="50"/>
+      <c r="C53" s="39"/>
+      <c r="D53" s="36" t="s">
+        <v>202</v>
+      </c>
+      <c r="E53" s="44"/>
+      <c r="F53" s="47"/>
     </row>
     <row r="54" ht="31" spans="1:6">
       <c r="A54" s="33"/>
       <c r="B54" s="33"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="38" t="s">
-        <v>206</v>
-      </c>
-      <c r="E54" s="49"/>
-      <c r="F54" s="50"/>
+      <c r="C54" s="39"/>
+      <c r="D54" s="36" t="s">
+        <v>203</v>
+      </c>
+      <c r="E54" s="44"/>
+      <c r="F54" s="47"/>
     </row>
     <row r="55" ht="16" spans="1:6">
       <c r="A55" s="33"/>
       <c r="B55" s="33"/>
-      <c r="C55" s="40"/>
-      <c r="D55" s="38" t="s">
-        <v>207</v>
-      </c>
-      <c r="E55" s="49"/>
-      <c r="F55" s="50"/>
+      <c r="C55" s="39"/>
+      <c r="D55" s="36" t="s">
+        <v>204</v>
+      </c>
+      <c r="E55" s="44"/>
+      <c r="F55" s="47"/>
     </row>
     <row r="56" ht="16" spans="1:6">
       <c r="A56" s="33"/>
       <c r="B56" s="33"/>
-      <c r="C56" s="40"/>
-      <c r="D56" s="38" t="s">
-        <v>208</v>
-      </c>
-      <c r="E56" s="49"/>
-      <c r="F56" s="50"/>
+      <c r="C56" s="39"/>
+      <c r="D56" s="36" t="s">
+        <v>205</v>
+      </c>
+      <c r="E56" s="44"/>
+      <c r="F56" s="47"/>
     </row>
     <row r="57" ht="16" spans="1:6">
       <c r="A57" s="33"/>
       <c r="B57" s="33"/>
-      <c r="C57" s="40"/>
-      <c r="D57" s="38" t="s">
-        <v>209</v>
-      </c>
-      <c r="E57" s="49"/>
-      <c r="F57" s="50"/>
+      <c r="C57" s="39"/>
+      <c r="D57" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="E57" s="44"/>
+      <c r="F57" s="47"/>
     </row>
     <row r="58" ht="16" spans="1:6">
       <c r="A58" s="33"/>
       <c r="B58" s="33"/>
-      <c r="C58" s="40"/>
-      <c r="D58" s="38" t="s">
-        <v>210</v>
-      </c>
-      <c r="E58" s="49"/>
-      <c r="F58" s="50"/>
+      <c r="C58" s="39"/>
+      <c r="D58" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="E58" s="44"/>
+      <c r="F58" s="47"/>
     </row>
     <row r="59" ht="16" spans="1:6">
       <c r="A59" s="33"/>
       <c r="B59" s="33"/>
-      <c r="C59" s="40"/>
-      <c r="D59" s="38" t="s">
-        <v>211</v>
-      </c>
-      <c r="E59" s="49"/>
-      <c r="F59" s="50"/>
+      <c r="C59" s="39"/>
+      <c r="D59" s="36" t="s">
+        <v>208</v>
+      </c>
+      <c r="E59" s="44"/>
+      <c r="F59" s="47"/>
     </row>
     <row r="60" ht="31" spans="1:6">
       <c r="A60" s="33"/>
       <c r="B60" s="33"/>
-      <c r="C60" s="40"/>
-      <c r="D60" s="38" t="s">
-        <v>212</v>
-      </c>
-      <c r="E60" s="49"/>
-      <c r="F60" s="50"/>
+      <c r="C60" s="39"/>
+      <c r="D60" s="36" t="s">
+        <v>209</v>
+      </c>
+      <c r="E60" s="44"/>
+      <c r="F60" s="47"/>
     </row>
     <row r="61" ht="92" spans="1:6">
       <c r="A61" s="33"/>
       <c r="B61" s="33"/>
-      <c r="C61" s="40"/>
+      <c r="C61" s="39"/>
       <c r="D61" s="36" t="s">
-        <v>213</v>
-      </c>
-      <c r="E61" s="49"/>
-      <c r="F61" s="50"/>
+        <v>210</v>
+      </c>
+      <c r="E61" s="44"/>
+      <c r="F61" s="47"/>
     </row>
     <row r="62" ht="16" spans="1:6">
       <c r="A62" s="33"/>
       <c r="B62" s="33"/>
-      <c r="C62" s="40"/>
-      <c r="D62" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="E62" s="49"/>
-      <c r="F62" s="50"/>
+      <c r="C62" s="39"/>
+      <c r="D62" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="E62" s="44"/>
+      <c r="F62" s="47"/>
     </row>
     <row r="63" ht="16" spans="1:6">
       <c r="A63" s="33"/>
       <c r="B63" s="33"/>
-      <c r="C63" s="40"/>
-      <c r="D63" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="E63" s="49"/>
-      <c r="F63" s="50"/>
+      <c r="C63" s="39"/>
+      <c r="D63" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="E63" s="44"/>
+      <c r="F63" s="47"/>
     </row>
     <row r="64" ht="16" spans="1:6">
       <c r="A64" s="33"/>
       <c r="B64" s="33"/>
-      <c r="C64" s="40"/>
-      <c r="D64" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="E64" s="49"/>
-      <c r="F64" s="50"/>
+      <c r="C64" s="39"/>
+      <c r="D64" s="36" t="s">
+        <v>213</v>
+      </c>
+      <c r="E64" s="44"/>
+      <c r="F64" s="47"/>
     </row>
     <row r="65" ht="16" spans="1:6">
       <c r="A65" s="33"/>
       <c r="B65" s="33"/>
-      <c r="C65" s="40"/>
-      <c r="D65" s="38" t="s">
-        <v>217</v>
-      </c>
-      <c r="E65" s="49"/>
-      <c r="F65" s="50"/>
+      <c r="C65" s="39"/>
+      <c r="D65" s="36" t="s">
+        <v>214</v>
+      </c>
+      <c r="E65" s="44"/>
+      <c r="F65" s="47"/>
     </row>
     <row r="66" ht="16" spans="1:6">
       <c r="A66" s="33"/>
       <c r="B66" s="33"/>
-      <c r="C66" s="40"/>
-      <c r="D66" s="38" t="s">
-        <v>218</v>
-      </c>
-      <c r="E66" s="49"/>
-      <c r="F66" s="50"/>
+      <c r="C66" s="39"/>
+      <c r="D66" s="36" t="s">
+        <v>215</v>
+      </c>
+      <c r="E66" s="44"/>
+      <c r="F66" s="47"/>
     </row>
     <row r="67" ht="31" spans="1:6">
       <c r="A67" s="33"/>
       <c r="B67" s="33"/>
-      <c r="C67" s="40"/>
-      <c r="D67" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="E67" s="49"/>
-      <c r="F67" s="50"/>
+      <c r="C67" s="39"/>
+      <c r="D67" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="E67" s="44"/>
+      <c r="F67" s="47"/>
     </row>
     <row r="68" ht="16" spans="1:6">
       <c r="A68" s="33"/>
       <c r="B68" s="33"/>
-      <c r="C68" s="40"/>
-      <c r="D68" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="E68" s="49"/>
-      <c r="F68" s="50"/>
+      <c r="C68" s="39"/>
+      <c r="D68" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="E68" s="44"/>
+      <c r="F68" s="47"/>
     </row>
     <row r="69" ht="16" spans="1:6">
       <c r="A69" s="33"/>
       <c r="B69" s="33"/>
-      <c r="C69" s="41"/>
-      <c r="D69" s="38" t="s">
-        <v>221</v>
-      </c>
-      <c r="E69" s="49"/>
-      <c r="F69" s="50"/>
+      <c r="C69" s="40"/>
+      <c r="D69" s="36" t="s">
+        <v>218</v>
+      </c>
+      <c r="E69" s="44"/>
+      <c r="F69" s="47"/>
     </row>
     <row r="70" ht="16" spans="1:6">
       <c r="A70" s="33"/>
       <c r="B70" s="33"/>
-      <c r="C70" s="42" t="s">
-        <v>222</v>
-      </c>
-      <c r="D70" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="E70" s="49"/>
-      <c r="F70" s="50"/>
+      <c r="C70" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="D70" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="E70" s="44"/>
+      <c r="F70" s="47"/>
     </row>
     <row r="71" ht="16" spans="1:6">
       <c r="A71" s="33"/>
       <c r="B71" s="33"/>
-      <c r="C71" s="43"/>
-      <c r="D71" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="E71" s="49"/>
-      <c r="F71" s="50"/>
+      <c r="C71" s="42"/>
+      <c r="D71" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="E71" s="44"/>
+      <c r="F71" s="47"/>
     </row>
     <row r="72" ht="16" spans="1:6">
       <c r="A72" s="33"/>
       <c r="B72" s="33"/>
-      <c r="C72" s="43"/>
-      <c r="D72" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="E72" s="49"/>
-      <c r="F72" s="50"/>
+      <c r="C72" s="42"/>
+      <c r="D72" s="36" t="s">
+        <v>222</v>
+      </c>
+      <c r="E72" s="44"/>
+      <c r="F72" s="47"/>
     </row>
     <row r="73" ht="47" customHeight="1" spans="1:6">
       <c r="A73" s="33"/>
       <c r="B73" s="33"/>
-      <c r="C73" s="43"/>
+      <c r="C73" s="42"/>
       <c r="D73" s="36" t="s">
-        <v>226</v>
-      </c>
-      <c r="E73" s="49"/>
-      <c r="F73" s="50"/>
+        <v>223</v>
+      </c>
+      <c r="E73" s="44"/>
+      <c r="F73" s="47"/>
     </row>
     <row r="74" ht="16" spans="1:6">
       <c r="A74" s="33"/>
       <c r="B74" s="33"/>
-      <c r="C74" s="43"/>
-      <c r="D74" s="38" t="s">
-        <v>227</v>
-      </c>
-      <c r="E74" s="49"/>
-      <c r="F74" s="50"/>
+      <c r="C74" s="42"/>
+      <c r="D74" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="E74" s="44"/>
+      <c r="F74" s="47"/>
     </row>
     <row r="75" ht="16" spans="1:6">
       <c r="A75" s="33"/>
       <c r="B75" s="33"/>
-      <c r="C75" s="43"/>
-      <c r="D75" s="38" t="s">
-        <v>228</v>
-      </c>
-      <c r="E75" s="49"/>
-      <c r="F75" s="50"/>
+      <c r="C75" s="42"/>
+      <c r="D75" s="36" t="s">
+        <v>225</v>
+      </c>
+      <c r="E75" s="44"/>
+      <c r="F75" s="47"/>
     </row>
     <row r="76" ht="16" spans="1:6">
       <c r="A76" s="33"/>
       <c r="B76" s="33"/>
-      <c r="C76" s="43"/>
-      <c r="D76" s="38" t="s">
-        <v>229</v>
-      </c>
-      <c r="E76" s="49"/>
-      <c r="F76" s="50"/>
+      <c r="C76" s="42"/>
+      <c r="D76" s="36" t="s">
+        <v>226</v>
+      </c>
+      <c r="E76" s="44"/>
+      <c r="F76" s="47"/>
     </row>
     <row r="77" ht="16" spans="1:6">
       <c r="A77" s="33"/>
       <c r="B77" s="33"/>
-      <c r="C77" s="43"/>
-      <c r="D77" s="38" t="s">
-        <v>230</v>
-      </c>
-      <c r="E77" s="49"/>
-      <c r="F77" s="50"/>
+      <c r="C77" s="42"/>
+      <c r="D77" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="E77" s="44"/>
+      <c r="F77" s="47"/>
     </row>
     <row r="78" ht="16" spans="1:6">
       <c r="A78" s="33"/>
       <c r="B78" s="33"/>
-      <c r="C78" s="43"/>
-      <c r="D78" s="38" t="s">
-        <v>231</v>
-      </c>
-      <c r="E78" s="49"/>
-      <c r="F78" s="50"/>
+      <c r="C78" s="42"/>
+      <c r="D78" s="36" t="s">
+        <v>228</v>
+      </c>
+      <c r="E78" s="44"/>
+      <c r="F78" s="47"/>
     </row>
     <row r="79" ht="16" spans="1:6">
       <c r="A79" s="33"/>
       <c r="B79" s="33"/>
-      <c r="C79" s="43"/>
-      <c r="D79" s="38" t="s">
-        <v>232</v>
-      </c>
-      <c r="E79" s="49"/>
-      <c r="F79" s="50"/>
+      <c r="C79" s="42"/>
+      <c r="D79" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="E79" s="44"/>
+      <c r="F79" s="47"/>
     </row>
     <row r="80" ht="16" spans="1:6">
       <c r="A80" s="33"/>
       <c r="B80" s="33"/>
-      <c r="C80" s="43"/>
-      <c r="D80" s="38" t="s">
-        <v>233</v>
-      </c>
-      <c r="E80" s="49"/>
-      <c r="F80" s="50"/>
+      <c r="C80" s="42"/>
+      <c r="D80" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="E80" s="44"/>
+      <c r="F80" s="47"/>
     </row>
     <row r="81" ht="31" spans="1:6">
       <c r="A81" s="33"/>
       <c r="B81" s="33"/>
-      <c r="C81" s="44"/>
-      <c r="D81" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="E81" s="49"/>
-      <c r="F81" s="50"/>
+      <c r="C81" s="43"/>
+      <c r="D81" s="36" t="s">
+        <v>231</v>
+      </c>
+      <c r="E81" s="44"/>
+      <c r="F81" s="47"/>
     </row>
     <row r="82" ht="16" spans="1:6">
       <c r="A82" s="33"/>
       <c r="B82" s="33"/>
-      <c r="C82" s="42" t="s">
-        <v>235</v>
-      </c>
-      <c r="D82" s="38" t="s">
-        <v>236</v>
-      </c>
-      <c r="E82" s="49"/>
-      <c r="F82" s="50"/>
+      <c r="C82" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="D82" s="36" t="s">
+        <v>233</v>
+      </c>
+      <c r="E82" s="44"/>
+      <c r="F82" s="47"/>
     </row>
     <row r="83" ht="16" spans="1:6">
       <c r="A83" s="33"/>
       <c r="B83" s="33"/>
-      <c r="C83" s="43"/>
-      <c r="D83" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="E83" s="49"/>
-      <c r="F83" s="50"/>
+      <c r="C83" s="42"/>
+      <c r="D83" s="36" t="s">
+        <v>234</v>
+      </c>
+      <c r="E83" s="44"/>
+      <c r="F83" s="47"/>
     </row>
     <row r="84" ht="43" customHeight="1" spans="1:6">
       <c r="A84" s="33"/>
       <c r="B84" s="33"/>
-      <c r="C84" s="43"/>
+      <c r="C84" s="42"/>
       <c r="D84" s="36" t="s">
-        <v>238</v>
-      </c>
-      <c r="E84" s="49"/>
-      <c r="F84" s="50"/>
+        <v>235</v>
+      </c>
+      <c r="E84" s="44"/>
+      <c r="F84" s="47"/>
     </row>
     <row r="85" ht="16" spans="1:6">
       <c r="A85" s="33"/>
       <c r="B85" s="33"/>
-      <c r="C85" s="43"/>
-      <c r="D85" s="38" t="s">
-        <v>239</v>
-      </c>
-      <c r="E85" s="49"/>
-      <c r="F85" s="50"/>
+      <c r="C85" s="42"/>
+      <c r="D85" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="E85" s="44"/>
+      <c r="F85" s="47"/>
     </row>
     <row r="86" ht="16" spans="1:6">
       <c r="A86" s="33"/>
       <c r="B86" s="33"/>
-      <c r="C86" s="43"/>
-      <c r="D86" s="38" t="s">
-        <v>240</v>
-      </c>
-      <c r="E86" s="49"/>
-      <c r="F86" s="50"/>
+      <c r="C86" s="42"/>
+      <c r="D86" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="E86" s="44"/>
+      <c r="F86" s="47"/>
     </row>
     <row r="87" ht="16" spans="1:6">
       <c r="A87" s="33"/>
       <c r="B87" s="33"/>
-      <c r="C87" s="43"/>
-      <c r="D87" s="38" t="s">
-        <v>241</v>
-      </c>
-      <c r="E87" s="49"/>
-      <c r="F87" s="50"/>
+      <c r="C87" s="42"/>
+      <c r="D87" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="E87" s="44"/>
+      <c r="F87" s="47"/>
     </row>
     <row r="88" ht="31" spans="1:6">
       <c r="A88" s="33"/>
       <c r="B88" s="33"/>
-      <c r="C88" s="44"/>
-      <c r="D88" s="38" t="s">
-        <v>242</v>
-      </c>
-      <c r="E88" s="49"/>
-      <c r="F88" s="50"/>
+      <c r="C88" s="43"/>
+      <c r="D88" s="36" t="s">
+        <v>239</v>
+      </c>
+      <c r="E88" s="44"/>
+      <c r="F88" s="47"/>
     </row>
     <row r="89" ht="31" spans="1:6">
       <c r="A89" s="33"/>
       <c r="B89" s="33"/>
-      <c r="C89" s="42" t="s">
-        <v>243</v>
-      </c>
-      <c r="D89" s="38" t="s">
-        <v>244</v>
-      </c>
-      <c r="E89" s="49"/>
-      <c r="F89" s="50"/>
+      <c r="C89" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="D89" s="36" t="s">
+        <v>241</v>
+      </c>
+      <c r="E89" s="44"/>
+      <c r="F89" s="47"/>
     </row>
     <row r="90" ht="61" spans="1:6">
       <c r="A90" s="33"/>
       <c r="B90" s="33"/>
-      <c r="C90" s="44"/>
-      <c r="D90" s="56" t="s">
-        <v>245</v>
-      </c>
-      <c r="E90" s="53"/>
-      <c r="F90" s="50"/>
+      <c r="C90" s="43"/>
+      <c r="D90" s="50" t="s">
+        <v>242</v>
+      </c>
+      <c r="E90" s="33"/>
+      <c r="F90" s="47"/>
     </row>
     <row r="91" ht="31" spans="1:6">
       <c r="A91" s="33"/>
       <c r="B91" s="33"/>
-      <c r="C91" s="42" t="s">
-        <v>246</v>
-      </c>
-      <c r="D91" s="38" t="s">
-        <v>247</v>
-      </c>
-      <c r="E91" s="49"/>
-      <c r="F91" s="50"/>
+      <c r="C91" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="D91" s="36" t="s">
+        <v>244</v>
+      </c>
+      <c r="E91" s="44"/>
+      <c r="F91" s="47"/>
     </row>
     <row r="92" ht="16" spans="1:6">
       <c r="A92" s="33"/>
       <c r="B92" s="33"/>
-      <c r="C92" s="43"/>
-      <c r="D92" s="38" t="s">
-        <v>248</v>
-      </c>
-      <c r="E92" s="49"/>
-      <c r="F92" s="50"/>
+      <c r="C92" s="42"/>
+      <c r="D92" s="36" t="s">
+        <v>245</v>
+      </c>
+      <c r="E92" s="44"/>
+      <c r="F92" s="47"/>
     </row>
     <row r="93" ht="16" spans="1:6">
       <c r="A93" s="33"/>
       <c r="B93" s="33"/>
-      <c r="C93" s="43"/>
-      <c r="D93" s="38" t="s">
-        <v>249</v>
-      </c>
-      <c r="E93" s="49"/>
-      <c r="F93" s="50"/>
+      <c r="C93" s="42"/>
+      <c r="D93" s="36" t="s">
+        <v>246</v>
+      </c>
+      <c r="E93" s="44"/>
+      <c r="F93" s="47"/>
     </row>
     <row r="94" ht="31" spans="1:6">
       <c r="A94" s="33"/>
       <c r="B94" s="33"/>
-      <c r="C94" s="43"/>
-      <c r="D94" s="38" t="s">
-        <v>250</v>
-      </c>
-      <c r="E94" s="49"/>
-      <c r="F94" s="50"/>
+      <c r="C94" s="42"/>
+      <c r="D94" s="36" t="s">
+        <v>247</v>
+      </c>
+      <c r="E94" s="44"/>
+      <c r="F94" s="47"/>
     </row>
     <row r="95" ht="16" spans="1:6">
       <c r="A95" s="33"/>
       <c r="B95" s="33"/>
-      <c r="C95" s="43"/>
-      <c r="D95" s="38" t="s">
-        <v>251</v>
-      </c>
-      <c r="E95" s="49"/>
-      <c r="F95" s="50"/>
+      <c r="C95" s="42"/>
+      <c r="D95" s="36" t="s">
+        <v>248</v>
+      </c>
+      <c r="E95" s="44"/>
+      <c r="F95" s="47"/>
     </row>
     <row r="96" ht="16" spans="1:6">
       <c r="A96" s="33"/>
       <c r="B96" s="33"/>
-      <c r="C96" s="43"/>
-      <c r="D96" s="38" t="s">
-        <v>252</v>
-      </c>
-      <c r="E96" s="49"/>
-      <c r="F96" s="50"/>
+      <c r="C96" s="42"/>
+      <c r="D96" s="36" t="s">
+        <v>249</v>
+      </c>
+      <c r="E96" s="44"/>
+      <c r="F96" s="47"/>
     </row>
     <row r="97" ht="16" spans="1:6">
       <c r="A97" s="33"/>
       <c r="B97" s="33"/>
-      <c r="C97" s="44"/>
-      <c r="D97" s="38" t="s">
-        <v>253</v>
-      </c>
-      <c r="E97" s="49"/>
-      <c r="F97" s="50"/>
+      <c r="C97" s="43"/>
+      <c r="D97" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="E97" s="44"/>
+      <c r="F97" s="47"/>
     </row>
     <row r="98" ht="16" spans="1:6">
       <c r="A98" s="33"/>
       <c r="B98" s="33"/>
-      <c r="C98" s="57"/>
-      <c r="D98" s="57" t="s">
-        <v>254</v>
-      </c>
-      <c r="E98" s="49"/>
-      <c r="F98" s="50"/>
+      <c r="C98" s="51"/>
+      <c r="D98" s="51" t="s">
+        <v>251</v>
+      </c>
+      <c r="E98" s="44"/>
+      <c r="F98" s="47"/>
     </row>
     <row r="99" ht="31" spans="1:6">
       <c r="A99" s="33"/>
       <c r="B99" s="33"/>
-      <c r="C99" s="56"/>
-      <c r="D99" s="56" t="s">
-        <v>255</v>
-      </c>
-      <c r="E99" s="49"/>
-      <c r="F99" s="50"/>
+      <c r="C99" s="50"/>
+      <c r="D99" s="50" t="s">
+        <v>252</v>
+      </c>
+      <c r="E99" s="44"/>
+      <c r="F99" s="47"/>
     </row>
     <row r="100" ht="16" spans="1:6">
       <c r="A100" s="33">
         <v>2</v>
       </c>
-      <c r="B100" s="58" t="s">
-        <v>256</v>
-      </c>
-      <c r="C100" s="59"/>
-      <c r="D100" s="59" t="s">
-        <v>257</v>
-      </c>
-      <c r="E100" s="49"/>
-      <c r="F100" s="50"/>
+      <c r="B100" s="52" t="s">
+        <v>253</v>
+      </c>
+      <c r="C100" s="53"/>
+      <c r="D100" s="53" t="s">
+        <v>254</v>
+      </c>
+      <c r="E100" s="44"/>
+      <c r="F100" s="47"/>
     </row>
     <row r="101" ht="16" spans="1:6">
       <c r="A101" s="33"/>
-      <c r="B101" s="58"/>
-      <c r="C101" s="60"/>
-      <c r="D101" s="60" t="s">
-        <v>258</v>
-      </c>
-      <c r="E101" s="49"/>
-      <c r="F101" s="50"/>
+      <c r="B101" s="52"/>
+      <c r="C101" s="54"/>
+      <c r="D101" s="54" t="s">
+        <v>255</v>
+      </c>
+      <c r="E101" s="44"/>
+      <c r="F101" s="47"/>
     </row>
     <row r="102" ht="16" spans="1:6">
       <c r="A102" s="33"/>
-      <c r="B102" s="58"/>
-      <c r="C102" s="61"/>
-      <c r="D102" s="61" t="s">
-        <v>259</v>
-      </c>
-      <c r="E102" s="49"/>
-      <c r="F102" s="50"/>
+      <c r="B102" s="52"/>
+      <c r="C102" s="55"/>
+      <c r="D102" s="55" t="s">
+        <v>256</v>
+      </c>
+      <c r="E102" s="44"/>
+      <c r="F102" s="47"/>
     </row>
     <row r="103" ht="16" spans="1:6">
       <c r="A103" s="33"/>
-      <c r="B103" s="58"/>
-      <c r="C103" s="60"/>
-      <c r="D103" s="60" t="s">
-        <v>260</v>
-      </c>
-      <c r="E103" s="49"/>
-      <c r="F103" s="50"/>
+      <c r="B103" s="52"/>
+      <c r="C103" s="54"/>
+      <c r="D103" s="54" t="s">
+        <v>257</v>
+      </c>
+      <c r="E103" s="44"/>
+      <c r="F103" s="47"/>
     </row>
     <row r="104" ht="16" spans="1:6">
       <c r="A104" s="33">
         <v>3</v>
       </c>
-      <c r="B104" s="58" t="s">
-        <v>261</v>
-      </c>
-      <c r="C104" s="60"/>
-      <c r="D104" s="60" t="s">
-        <v>262</v>
-      </c>
-      <c r="E104" s="49"/>
-      <c r="F104" s="50"/>
+      <c r="B104" s="52" t="s">
+        <v>258</v>
+      </c>
+      <c r="C104" s="54"/>
+      <c r="D104" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="E104" s="44"/>
+      <c r="F104" s="47"/>
     </row>
     <row r="105" ht="31" spans="1:6">
       <c r="A105" s="33"/>
-      <c r="B105" s="58"/>
-      <c r="C105" s="60"/>
-      <c r="D105" s="60" t="s">
-        <v>263</v>
-      </c>
-      <c r="E105" s="49"/>
-      <c r="F105" s="50"/>
+      <c r="B105" s="52"/>
+      <c r="C105" s="54"/>
+      <c r="D105" s="54" t="s">
+        <v>260</v>
+      </c>
+      <c r="E105" s="44"/>
+      <c r="F105" s="47"/>
     </row>
     <row r="106" ht="16" spans="1:6">
       <c r="A106" s="33"/>
-      <c r="B106" s="58"/>
-      <c r="C106" s="60"/>
-      <c r="D106" s="60" t="s">
-        <v>264</v>
-      </c>
-      <c r="E106" s="49"/>
-      <c r="F106" s="50"/>
+      <c r="B106" s="52"/>
+      <c r="C106" s="54"/>
+      <c r="D106" s="54" t="s">
+        <v>261</v>
+      </c>
+      <c r="E106" s="44"/>
+      <c r="F106" s="47"/>
     </row>
     <row r="107" ht="56" customHeight="1" spans="1:6">
       <c r="A107" s="33"/>
-      <c r="B107" s="58"/>
-      <c r="C107" s="61"/>
-      <c r="D107" s="61" t="s">
-        <v>265</v>
-      </c>
-      <c r="E107" s="49"/>
-      <c r="F107" s="50"/>
+      <c r="B107" s="52"/>
+      <c r="C107" s="55"/>
+      <c r="D107" s="55" t="s">
+        <v>262</v>
+      </c>
+      <c r="E107" s="44"/>
+      <c r="F107" s="47"/>
     </row>
     <row r="108" ht="16" spans="1:6">
       <c r="A108" s="33"/>
-      <c r="B108" s="58"/>
-      <c r="C108" s="60"/>
-      <c r="D108" s="60" t="s">
-        <v>266</v>
-      </c>
-      <c r="E108" s="49"/>
-      <c r="F108" s="50"/>
+      <c r="B108" s="52"/>
+      <c r="C108" s="54"/>
+      <c r="D108" s="54" t="s">
+        <v>263</v>
+      </c>
+      <c r="E108" s="44"/>
+      <c r="F108" s="47"/>
     </row>
     <row r="109" ht="16" spans="1:6">
       <c r="A109" s="33">
         <v>4</v>
       </c>
       <c r="B109" s="33" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C109" s="30"/>
       <c r="D109" s="30" t="s">
-        <v>267</v>
-      </c>
-      <c r="E109" s="49"/>
-      <c r="F109" s="50"/>
+        <v>264</v>
+      </c>
+      <c r="E109" s="44"/>
+      <c r="F109" s="47"/>
     </row>
     <row r="110" ht="16" spans="1:6">
       <c r="A110" s="33"/>
       <c r="B110" s="33"/>
-      <c r="C110" s="62"/>
-      <c r="D110" s="62" t="s">
-        <v>258</v>
-      </c>
-      <c r="E110" s="49"/>
-      <c r="F110" s="50"/>
+      <c r="C110" s="56"/>
+      <c r="D110" s="56" t="s">
+        <v>255</v>
+      </c>
+      <c r="E110" s="44"/>
+      <c r="F110" s="47"/>
     </row>
     <row r="111" ht="16" spans="1:6">
       <c r="A111" s="33"/>
       <c r="B111" s="33"/>
-      <c r="C111" s="62"/>
-      <c r="D111" s="62" t="s">
-        <v>268</v>
-      </c>
-      <c r="E111" s="49"/>
-      <c r="F111" s="50"/>
+      <c r="C111" s="56"/>
+      <c r="D111" s="56" t="s">
+        <v>265</v>
+      </c>
+      <c r="E111" s="44"/>
+      <c r="F111" s="47"/>
     </row>
     <row r="112" ht="16" spans="1:6">
       <c r="A112" s="33"/>
       <c r="B112" s="33"/>
-      <c r="C112" s="62"/>
-      <c r="D112" s="62" t="s">
-        <v>269</v>
-      </c>
-      <c r="E112" s="49"/>
-      <c r="F112" s="50"/>
+      <c r="C112" s="56"/>
+      <c r="D112" s="56" t="s">
+        <v>266</v>
+      </c>
+      <c r="E112" s="44"/>
+      <c r="F112" s="47"/>
     </row>
     <row r="113" ht="16" spans="1:6">
       <c r="A113" s="33"/>
       <c r="B113" s="33"/>
-      <c r="C113" s="62"/>
-      <c r="D113" s="62" t="s">
-        <v>270</v>
-      </c>
-      <c r="E113" s="49"/>
-      <c r="F113" s="50"/>
+      <c r="C113" s="56"/>
+      <c r="D113" s="56" t="s">
+        <v>267</v>
+      </c>
+      <c r="E113" s="44"/>
+      <c r="F113" s="47"/>
     </row>
     <row r="114" ht="16" spans="1:6">
       <c r="A114" s="33"/>
       <c r="B114" s="33"/>
-      <c r="C114" s="62"/>
-      <c r="D114" s="62" t="s">
-        <v>271</v>
-      </c>
-      <c r="E114" s="49"/>
-      <c r="F114" s="50"/>
+      <c r="C114" s="56"/>
+      <c r="D114" s="56" t="s">
+        <v>268</v>
+      </c>
+      <c r="E114" s="44"/>
+      <c r="F114" s="47"/>
     </row>
     <row r="115" ht="16" spans="1:6">
       <c r="A115" s="33"/>
       <c r="B115" s="33"/>
-      <c r="C115" s="62"/>
-      <c r="D115" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E115" s="49"/>
-      <c r="F115" s="50"/>
+      <c r="C115" s="56"/>
+      <c r="D115" s="56" t="s">
+        <v>269</v>
+      </c>
+      <c r="E115" s="44"/>
+      <c r="F115" s="47"/>
     </row>
     <row r="116" ht="16" spans="1:6">
       <c r="A116" s="33">
         <v>5</v>
       </c>
       <c r="B116" s="33" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C116" s="30"/>
       <c r="D116" s="30" t="s">
-        <v>274</v>
-      </c>
-      <c r="E116" s="49"/>
-      <c r="F116" s="50"/>
+        <v>271</v>
+      </c>
+      <c r="E116" s="44"/>
+      <c r="F116" s="47"/>
     </row>
     <row r="117" ht="16" spans="1:6">
       <c r="A117" s="33"/>
       <c r="B117" s="33"/>
-      <c r="C117" s="62"/>
-      <c r="D117" s="62" t="s">
-        <v>258</v>
-      </c>
-      <c r="E117" s="49"/>
-      <c r="F117" s="50"/>
+      <c r="C117" s="56"/>
+      <c r="D117" s="56" t="s">
+        <v>255</v>
+      </c>
+      <c r="E117" s="44"/>
+      <c r="F117" s="47"/>
     </row>
     <row r="118" ht="16" spans="1:6">
       <c r="A118" s="33"/>
       <c r="B118" s="33"/>
-      <c r="C118" s="62"/>
-      <c r="D118" s="62" t="s">
-        <v>275</v>
-      </c>
-      <c r="E118" s="49"/>
-      <c r="F118" s="50"/>
+      <c r="C118" s="56"/>
+      <c r="D118" s="56" t="s">
+        <v>272</v>
+      </c>
+      <c r="E118" s="44"/>
+      <c r="F118" s="47"/>
     </row>
     <row r="119" ht="16" spans="1:6">
       <c r="A119" s="33"/>
       <c r="B119" s="33"/>
-      <c r="C119" s="62"/>
-      <c r="D119" s="62" t="s">
-        <v>276</v>
-      </c>
-      <c r="E119" s="49"/>
-      <c r="F119" s="50"/>
+      <c r="C119" s="56"/>
+      <c r="D119" s="56" t="s">
+        <v>273</v>
+      </c>
+      <c r="E119" s="44"/>
+      <c r="F119" s="47"/>
     </row>
     <row r="120" ht="16" spans="1:6">
       <c r="A120" s="33"/>
       <c r="B120" s="33"/>
-      <c r="C120" s="62"/>
-      <c r="D120" s="62" t="s">
-        <v>277</v>
-      </c>
-      <c r="E120" s="49"/>
-      <c r="F120" s="50"/>
+      <c r="C120" s="56"/>
+      <c r="D120" s="56" t="s">
+        <v>274</v>
+      </c>
+      <c r="E120" s="44"/>
+      <c r="F120" s="47"/>
     </row>
     <row r="121" ht="16" spans="1:6">
       <c r="A121" s="33"/>
       <c r="B121" s="33"/>
-      <c r="C121" s="62"/>
-      <c r="D121" s="62" t="s">
-        <v>271</v>
-      </c>
-      <c r="E121" s="49"/>
-      <c r="F121" s="50"/>
+      <c r="C121" s="56"/>
+      <c r="D121" s="56" t="s">
+        <v>268</v>
+      </c>
+      <c r="E121" s="44"/>
+      <c r="F121" s="47"/>
     </row>
     <row r="122" ht="16" spans="1:6">
       <c r="A122" s="33"/>
       <c r="B122" s="33"/>
-      <c r="C122" s="62"/>
-      <c r="D122" s="62" t="s">
-        <v>278</v>
-      </c>
-      <c r="E122" s="49"/>
-      <c r="F122" s="50"/>
+      <c r="C122" s="56"/>
+      <c r="D122" s="56" t="s">
+        <v>275</v>
+      </c>
+      <c r="E122" s="44"/>
+      <c r="F122" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -7027,20 +6594,20 @@
   <sheetData>
     <row r="1" ht="154" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" ht="17.25" customHeight="1" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" ht="71.75" spans="1:3">
@@ -7048,159 +6615,159 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" ht="18.75" spans="1:3">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="7" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" ht="36.75" spans="1:3">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="8" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" ht="36.75" spans="1:3">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="9" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" ht="18.75" spans="1:3">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="8" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" ht="18.75" spans="1:3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="10" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9" ht="18.75" spans="1:3">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="10" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1" spans="1:3">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" ht="71.75" spans="1:3">
       <c r="A11" s="4"/>
       <c r="B11" s="5" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="12" ht="18.75" spans="1:3">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" ht="18.75" spans="1:3">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="10" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14" ht="18.75" spans="1:3">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="10" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" ht="18.75" spans="1:3">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="10" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="16" ht="18.75" spans="1:3">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="10" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" ht="18.75" spans="1:3">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="10" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="18" ht="18.75" spans="1:3">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="10" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="19" ht="18.75" spans="1:3">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="10" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="20" ht="18.75" spans="1:3">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="10" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="21" ht="18.75" spans="1:3">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="22" ht="18.75" spans="1:3">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="9" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="23" ht="18.75" spans="1:3">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="10" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="24" ht="33" customHeight="1" spans="1:3">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1" spans="1:3">
@@ -7208,40 +6775,40 @@
         <v>2</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="26" ht="18.75" spans="1:3">
       <c r="A26" s="4"/>
       <c r="B26" s="13" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="27" ht="18.75" spans="1:3">
       <c r="A27" s="4"/>
       <c r="B27" s="14"/>
       <c r="C27" s="10" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="28" ht="18.75" spans="1:3">
       <c r="A28" s="4"/>
       <c r="B28" s="14"/>
       <c r="C28" s="10" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1" spans="1:3">
       <c r="A29" s="4"/>
       <c r="B29" s="15"/>
       <c r="C29" s="16" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="30" ht="18.75" spans="1:3">
@@ -7249,24 +6816,24 @@
         <v>3</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>52</v>
+        <v>312</v>
       </c>
     </row>
     <row r="31" ht="18.75" spans="1:3">
       <c r="A31" s="4"/>
       <c r="B31" s="19"/>
       <c r="C31" s="20" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1" spans="1:3">
       <c r="A32" s="4"/>
       <c r="B32" s="19"/>
       <c r="C32" s="21" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="33" ht="18.75" spans="1:3">
@@ -7274,54 +6841,54 @@
         <v>4</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="34" ht="18.75" spans="1:3">
       <c r="A34" s="4"/>
       <c r="B34" s="22" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="35" ht="18.75" spans="1:3">
       <c r="A35" s="4"/>
       <c r="B35" s="24"/>
       <c r="C35" s="20" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="36" ht="18.75" spans="1:3">
       <c r="A36" s="4"/>
       <c r="B36" s="24"/>
       <c r="C36" s="20" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="37" ht="18.75" spans="1:3">
       <c r="A37" s="4"/>
       <c r="B37" s="24"/>
       <c r="C37" s="20" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="38" ht="18.75" spans="1:3">
       <c r="A38" s="4"/>
       <c r="B38" s="24"/>
       <c r="C38" s="20" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="39" ht="17.25" customHeight="1" spans="1:3">
       <c r="A39" s="4"/>
       <c r="B39" s="25"/>
       <c r="C39" s="21" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="40" ht="18.75" spans="1:3">
@@ -7329,59 +6896,59 @@
         <v>5</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="41" ht="36.75" spans="1:3">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="10" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="42" ht="36.75" spans="1:3">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="10" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="43" ht="18.75" spans="1:3">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="10" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="44" ht="18.75" spans="1:3">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="10" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="45" ht="36.75" spans="1:3">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="26" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="46" ht="36.75" spans="1:3">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="10" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="47" ht="17.25" customHeight="1" spans="1:3">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="16" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="48" ht="36.75" spans="1:3">
@@ -7389,38 +6956,38 @@
         <v>6</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="49" ht="36.75" spans="1:3">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="26" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="50" ht="18.75" spans="1:3">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="10" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="51" ht="18.75" spans="1:3">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="26" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="52" ht="18.75" spans="1:3">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="12" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
